--- a/saida/produtos_enriquecidos_parte_4.xlsx
+++ b/saida/produtos_enriquecidos_parte_4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Tipo: Perfil U Enrijecido, Processo de Fabricação: Fino a Quente (laminado a quente), Largura da base: 40 mm, Espessura: 2,00 mm, Comprimento: 6 metros, Peso: 18 kg por unidade.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://loja.acocearense.com.br/perfil-de-aco-u-enrijecido-fino-a-quente-4-40mm-200mm-6m/p</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3634,7 +3634,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://acocearense.vtexassets.com/arquivos/ids/156194-1440-auto/perfil-enrijecido.webp?v=638548009695030000&amp;quality=8 | https://acocearense.vtexassets.com/arquivos/ids/156194-154-auto/perfil-enrijecido.webp?v=638548009695030000&amp;quality=8 | https://acocearense.vtexassets.com/arquivos/ids/156582-154-auto/FERFIL_U_ENRIJECIDO_POSI_03-800x600.webp?v=638920027949470000&amp;quality=8</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3669,20 +3673,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Formato: Perfil estrutural monossimétrico com faces de aba não paralelas e inclinação interna de aproximadamente 16,67%. Material: Aço carbono. Processo de fabricação: Laminação a quente. Aplicações: Serralheria, estruturas metálicas, carrocerias de ônibus, implementos agrícolas, construção civil. Normas: NBR 7007, ASTM A36, NBR 15980.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://conexao.arcelormittal.com.br/produtos/perfil-u</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>https://www.novacaledonia.com.br/wp-content/uploads/2024/11/informativo-tecnico-perfil-u-enrijecido.pdf</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://conexao.arcelormittal.com.br/files/photos/86f6e2e8-a7ea-4314-8a87-e6883a4e6c13?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/c58985af-03a7-4960-8252-8ba9220ee4f2?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/a68cc73a-f7fa-405c-a5b3-aff0e53f013c?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/8feb002e-3fa1-4865-83c7-df443da67bfe?height=489&amp;width=795</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3717,12 +3725,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Formato: Perfil estrutural monossimétrico, com faces de aba não paralelas e inclinação interna das abas de aproximadamente 16,67% (inclinação entre 9º e 10º). Material: Aço carbono. Processo de fabricação: Laminação a quente. Aplicações: Serralheria, estruturas metálicas, carrocerias de ônibus, implementos agrícolas e construção civil. Versatilidade: Pode ser cortado, furado, soldado e conectado. Normas: NBR 7007, ASTM A36 e NBR 15980.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://conexao.arcelormittal.com.br/produtos/perfil-u</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3730,7 +3738,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://conexao.arcelormittal.com.br/files/photos/86f6e2e8-a7ea-4314-8a87-e6883a4e6c13?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/c58985af-03a7-4960-8252-8ba9220ee4f2?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/a68cc73a-f7fa-405c-a5b3-aff0e53f013c?height=489&amp;width=795 | https://conexao.arcelormittal.com.br/files/photos/8feb002e-3fa1-4865-83c7-df443da67bfe?height=489&amp;width=795</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3765,12 +3777,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Dimensões: 50x25x10x2,00 a 150x60x20x3,00 mm. Peso teórico por metro: 1,38 kg/m a 6,75 kg/m. Comprimento máximo: 6 metros. Espessura: 2,00 mm a 4,75 mm.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://ciadoferro.com.br/perfil-u/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3778,7 +3790,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://ciadoferro.com.br/wp-content/uploads/2022/03/perfiludc-01-1024x659.png</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3811,11 +3827,7 @@
           <t>Kit de segurança e acesso, composto por diversos componentes para controle de acesso e monitoramento de segurança.</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -3861,12 +3873,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Sensor de imagem: 4 x CMOS RGB de 1/2” com varredura progressiva, tamanho do pixel 2,9 μm. Lente: 3,7 mm, F2.0. Campo de visão horizontal: 360°, 108,4° para cada sensor. Campo de visão vertical: 84°. Distância de foco mínima: 1.0 m (3.3 ft). Filtro de bloqueio de IR automático. Iluminação mínima: Cor: 0,06 lux a 50 IRE, F2.0; P/B: 0,03 lux a 50 IRE, F2.0. Velocidade do obturador: 1/66500 s a 2 s. Ajuste da câmera: Pan ±180°, tilt -40 a +75°, rotação ±95°. Sistema em um chip (SoC): ARTPEC-8 (x2). Memória: 8 GB de RAM, 8 GB de flash.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.axis.com/dam/public/0b/4b/de/datasheet-axis-q6020-e-panoramic-camera-pt-BR-505672.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3909,12 +3921,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Câmera dome fixa de 2 MP, AXIS License Plate Verifier pré-instalado, suporte a listas de permissão e bloqueio, resistente a vandalismo, Axis OptimizedIR, suporte interno para controladores de porta em rede Axis.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.axis.com/dam/public/a5/5e/3e/datasheet-axis-p3265-lve-3-license-plate-verifier-kit-pt-BR-432535.pdf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3922,7 +3934,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://propacusa.com/_assets/images/products/K20113-E/K20113-Pro3.jpg | https://epaluminio.com.br/wp-content/uploads/2018/06/CH-KITS-03.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8080,7 +8096,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tubo Metalon com dimensões 150 x 50 x 16. Produto não encontrado na web.</t>
+          <t>Tubo Metalon 150 x 50 x 16, um perfil tubular de aço carbono com seção quadrada, fabricado com costura por solda longitudinal, usado em estruturas metálicas, serralheria, portões, móveis e máquinas.</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -8090,12 +8106,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.tubonasa.com.br/tubos-quadrados</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.allitubos.com.br/tabelas/allitubos-catalogo-tubos-metalon.pdf</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -9328,7 +9344,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tubo Metalon com dimensões 50 x 30 x 16. Produto não encontrado na web.</t>
+          <t>O Metalon 50x30 é um tubo de aço retangular, amplamente utilizado em serralheria, especialmente para portões e grades. Disponível em diferentes espessuras, sendo as mais comuns 1,50 mm (chapa 16) e 2,00 mm (chapa 14).</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -9338,7 +9354,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.tubonasa.com.br/metalon-50x30</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9346,7 +9362,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://66882.cdn.simplo7.net/static/66882/sku/tubos-metalon-50-x-30-chapa-16-1-50mm-x-6000mm-p-1731696064229.png | https://66882.cdn.simplo7.net/static/66882/sku/tubos-metalon-50-x-30-chapa-16-1-50mm-x-6000mm-p-1731696073219.png</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10384,7 +10404,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tubo Metalon com dimensões 70 x 30 x 16. Produto não encontrado na web.</t>
+          <t>O Metalon Retangular Fino a Frio 70mm x 30mm com espessura de 1,50mm 6 metros é uma excelente escolha para projetos que exigem resistência estrutural, precisão dimensional e acabamento de alta qualidade. Fabricado em aço carbono por meio do processo de laminação a frio, oferece superfície uniforme, excelente soldabilidade e maior rigor dimensional.</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10394,7 +10414,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://loja.acocearense.com.br/tubo-de-aco-retangular-fino-a-frio-70mm-30mm-150mm-6m/p</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10402,7 +10422,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/964419/tubo_retangular_lf_70_x_30_16_1_50mm_1863_1_036da460c1e3a1f59b535b2e300be6ab.jpg | https://http2.mlstatic.com/D_Q_NP_2X_622037-MLA96668785987_102025-P.webp | https://http2.mlstatic.com/D_NQ_NP_628205-MLB96498179195_102025-O-metalon-70x30-tubo-retangular-de-aco--3-pecas-de-100-metro.webp</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11152,7 +11176,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tubo Metalon com dimensões 90 x 30 x 16. Produto não encontrado na web.</t>
+          <t>Tubo Metalon 90 x 30 x 16 é um perfil tubular de aço carbono com seção retangular, fabricado com costura por solda longitudinal. Utilizado em estruturas metálicas, serralheria, portões, móveis e máquinas.</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -11162,15 +11186,19 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.tubonasa.com.br/tubos-quadrados</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr"/>
+          <t>https://www.allitubos.com.br/tabelas/allitubos-catalogo-tubos-metalon.pdf</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/964419/tubo_retangular_lf_70_x_30_16_1_50mm_1863_1_036da460c1e3a1f59b535b2e300be6ab.jpg | https://http2.mlstatic.com/D_NQ_NP_775728-MLB70970012237_082023-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13888,17 +13916,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>O produto SUCATA F é um tipo de sucata metálica, geralmente composta por peças de aço carbono com dimensões superiores a 0,80 cm, incluindo tratores, tanques, grandes estruturas, chapas, vigas, tubos e perfis.</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Composto por peças de aço carbono; Dimensões superiores a 0,80 cm; Inclui tratores, tanques, grandes estruturas, chapas, vigas, tubos e perfis.</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.pmgambiental.com.br/sucata</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -13906,7 +13934,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr"/>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://static.wixstatic.com/media/77743a_27d7da2c3ce04796963b9ee394737741~mv2.png/v1/fill/w_1905,h_959,al_c,q_90,usm_0.66_1.00_0.01,enc_avif,quality_auto/77743a_27d7da2c3ce04796963b9ee394737741~mv2.png | https://static.wixstatic.com/media/77743a_ca3ddb2430ae47fbaec35c13f8d344bf~mv2.png/v1/fill/w_1068,h_580,al_c,q_90,usm_0.66_1.00_0.01,enc_avif,quality_auto/Sem%20nome%20(Site)%20(5).png</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14181,12 +14213,12 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Couro nobuk preto, biqueira de aço, solado de poliuretano bidensidade, resistência ao óleo e combustível, forro interno em TNT, palmilha de montagem em TNT resinado na cor branca, fechamento em cadarço.</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.balaska.com.br/en/botina-marluvas-50b22m-a-amarrar-new-prime-bico-aco-preto</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -14194,7 +14226,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr"/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://d1ql0a3e3j9mcx.cloudfront.net/Custom/Content/Products/83/74/8374_botina-new-prime-marluvas-de-amarrar-nobuck-marrom-preta-50b26cbbp_z5_638957082325892506.webp | https://d1ql0a3e3j9mcx.cloudfront.net/Custom/Content/Products/83/74/8374_botina-new-prime-marluvas-de-amarrar-nobuck-marrom-preta-50b26cbbp_l3_638120751651513896.webp</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14224,17 +14260,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Bota Cadac Nobuk New Prime na cor preta, tamanho 41. Produto não encontrado na web.</t>
+          <t>Bota de segurança New Prime da Marluvas, modelo Nobuk, na cor preta, tamanho 41. Confeccionada em couro nobuck com biqueira de aço e solado de poliuretano bidensidade.</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Calçado de segurança, tipo botina, com fechamento em cadarço, confeccionado em couro preto curtido ao cromo, palmilha de montagem em TNT – Tecido não tecido resinado na cor branca, costurada pelo processo strobel, forro interno em TNT tecido não tecido na cor cinza, solado em poliuretano bidensidade, injetado diretamente ao cabedal na cor preta, com resistência ao óleo combustível e a absorção de energia no salto, biqueira de aço.</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.fmferragens.com.br/produto/bota-c-cadarco-nobuck-cafe-new-prime-no-41-700611-41-marluvas-12000</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -14242,7 +14278,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://d1ql0a3e3j9mcx.cloudfront.net/Custom/Content/Products/83/74/8374_botina-new-prime-marluvas-de-amarrar-nobuck-marrom-preta-50b26cbbp_z5_638957082325892506.webp | https://static.lojabrafer.com.br/public/brafer/imagens/produtos/botina-de-couro-nobuck-coturno-militar-41-qap-preto-prowork-68d5a3cf8debe.png</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14325,12 +14365,12 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Biqueira de composite leve, antimagnética, anticorrosiva e ultraresistente; Fechamento em elástico; Palmilha de montagem têxtil resistente à perfuração; Solado isolante em PU bidensidade bicolor com sistema de absorção de impacto; Confeccionada em microfibra preta; Numeração: 35 ao 47.</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.marluvas.com.br/en</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -14338,7 +14378,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://atacadaodoepi.com.br/wp-content/uploads/2023/05/47225.jpg | https://cdn.awsli.com.br/1242/1242395/produto/304302822/124b56b64e6e38929b74ec3924f3b81f-0mvfkowewy.jpg | https://cdn.awsli.com.br/1242/1242395/produto/304302822/b1e05a3d3d7cc712f690e1e91dd1e2ef-f8fqisgbty.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14467,11 +14511,7 @@
           <t>Bota com elástico no tamanho 42.</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14515,11 +14555,7 @@
           <t>Bota elástica tamanho 42 da marca Marluvias.</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14563,11 +14599,7 @@
           <t>Bota elástica tamanho 42, CA 47225, da marca Marluvast EPI.</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14611,11 +14643,7 @@
           <t>Bota com elástico no tamanho 43.</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14661,20 +14689,24 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>Calçado de segurança tipo botina, fechamento em elástico, confeccionado em couro preto curtido ao cromo, palmilha de montagem em material sintético resinado na cor branca costurado pelo sistema strobel, forro interno em não tecido na cor cinza, solado bicomponente de borracha e poliuretano injetado diretamente no cabedal, biqueira de composite, resistente ao óleo combustível, à absorção de energia no calcanhar, ao contato com o calor e à passagem de corrente elétrica. Aprovado para proteção dos pés do usuário contra impactos de quedas de objetos sobre os artelhos, contra agentes abrasivos e escoriantes e contra choques elétricos. Tamanho: 33 ao 47.</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://www.marluvas.com.br/en</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr"/>
+          <t>https://www.scribd.com/document/722476303/CA-13808-CALCADO-TIPO-BOTINA-MARLUVAS-EQUIPAMENTOS-DE-SEGURANCA-LTDA</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/600x1000/1242/1242395/produto/302399861/botina-bota-de-seguranca-p-trabalho-bidensidade-marluvas-vulcaflex-10vb48_3183---i0wxgvqyqw.jpeg | https://acdn-us.mitiendanube.com/stores/007/007/418/products/botina_de_seguran_a_microfibra_eletricista_70b19e-bp_marluvas_n_43_ferpam-d5ebc88e895a8fa55517831558938108-1024-1024.webp | https://dimensionalstoreb2b.vtexassets.com/arquivos/ids/215689/95B19Bp-MARLUVAS-2.png?v=638340270775130000</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">

--- a/saida/produtos_enriquecidos_parte_4.xlsx
+++ b/saida/produtos_enriquecidos_parte_4.xlsx
@@ -14739,11 +14739,7 @@
           <t>Bota elástica tamanho 43, CA 47225, da marca Marluvast EPI.</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -14835,11 +14831,7 @@
           <t>Bota elástica tamanho 45, CA 47225, da marca Marluvast EPI.</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15267,11 +15259,7 @@
           <t>Bota elástica de segurança com ponta de aço, cor preta, tamanho 40, modelo 1103 da marca DALLAS.</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15315,11 +15303,7 @@
           <t>Bota elástica de segurança PU preta, tamanho 41, modelo 1103 da marca Dallas.</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15411,11 +15395,7 @@
           <t>Bota elástica da marca Marluvias, tamanho 40, com bico normal.</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15507,11 +15487,7 @@
           <t>Bota elástica da marca Marluvias, tamanho 41, com bico normal.</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15603,11 +15579,7 @@
           <t>Bota elástica da marca Marluvias, tamanho 42, com bico normal.</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15747,11 +15719,7 @@
           <t>Bota elástica da marca Marluvos, tamanho 44.</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -15891,11 +15859,7 @@
           <t>Bota EPI Velcro Nobuk Cafe, tamanho 39, modelo CA 43273 da marca Marluvias.</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16179,11 +16143,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc anti-chamas, tamanho 40, cor preta.</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16227,11 +16187,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Anti-Flamas, tamanho 41, cor preta.</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16275,11 +16231,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc anti-chamas, tamanho 42, cor preta.</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16323,11 +16275,7 @@
           <t>Bota de segurança da marca Cadarc, modelo Nobuk, cor café, tamanho 40, da linha Kala.</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16371,11 +16319,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor café, tamanho 40.</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16419,11 +16363,7 @@
           <t>Bota de segurança da marca Cadarc, modelo Nobuk, cor café, tamanho 41, da linha Kala.</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16467,11 +16407,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk Café, tamanho 41.</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16515,11 +16451,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor café, tamanho 42.</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16563,11 +16495,7 @@
           <t>Bota de segurança da marca Cadarc, modelo Nobuk, cor café, tamanho 43, da linha Kala.</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16611,11 +16539,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk Café, tamanho 43.</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16659,11 +16583,7 @@
           <t>Bota de segurança da marca Marluvas, modelo Cadarc Nubuk Castor, tamanho 42.</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16707,11 +16627,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor cinza, tamanho 40.</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16755,11 +16671,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor cinza, tamanho 41.</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16803,11 +16715,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor cinza, tamanho 42.</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16851,11 +16759,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor cinza, tamanho 43.</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16899,11 +16803,7 @@
           <t>Bota de segurança da marca Kala, modelo Cadarc Nubuk, cor preta, tamanho 40.</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16947,11 +16847,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor preta, tamanho 40.</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -16995,11 +16891,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk na cor preta, tamanho 41.</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17043,11 +16935,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk, cor preta, tamanho 42.</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17091,11 +16979,7 @@
           <t>Bota de segurança da marca Kala, modelo CADARC NOBUK na cor preta, tamanho 43.</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17139,11 +17023,7 @@
           <t>Bota de segurança da marca Marluvast, modelo Cadarc Nubuk, cor preta, tamanho 43.</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17187,11 +17067,7 @@
           <t>Bota de segurança da marca Cadarc, modelo Vaqueta, na cor chocolate e tamanho 40, fabricada pela Dalllas.</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17235,11 +17111,7 @@
           <t>Bota de segurança da marca Brand, cor chocolate, tamanho 39.</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17283,11 +17155,7 @@
           <t>Bota de segurança da marca Dallas, cor chocolate, tamanho 40.</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17331,11 +17199,7 @@
           <t>Bota de segurança da marca Brand, cor chocolate, tamanho 41, modelo Dallas.</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17379,11 +17243,7 @@
           <t>Bota de segurança da marca Brand, cor chocolate, tamanho 42, modelo Dallas.</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17427,11 +17287,7 @@
           <t>Bota de segurança da marca Brand, cor chocolate, tamanho 43, modelo Dallas.</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17715,11 +17571,7 @@
           <t>Bota de segurança com fechamento em velcro, fabricada em material nobuck na cor café, tamanho 43, da marca Marluvaz.</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17811,11 +17663,7 @@
           <t>Bota de segurança com fechamento em velcro, material em nobuck na cor preta, tamanho 39, da marca Marluvast.</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -17955,11 +17803,7 @@
           <t>Bota de segurança com fechamento em velcro, fabricada em material nobuck na cor preta, tamanho 42, da marca Marluvaseg.</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18099,11 +17943,7 @@
           <t>Bota de segurança com fechamento em velcro, fabricada pela Dallas, na cor café e tamanho 40.</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18243,11 +18083,7 @@
           <t>Bota de segurança com fechamento em velcro, material em PU, cor café, tamanho 43.</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18339,11 +18175,7 @@
           <t>Bota de segurança preta com fechamento em velcro, tamanho 40, modelo 1153 da marca DALLAS.</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18531,11 +18363,7 @@
           <t>Capa de chuva G CA 28191, um Equipamento de Proteção Individual (EPI) para uso em ambientes de trabalho.</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18574,16 +18402,8 @@
           <t>MATERIAL DE SEGURANCA</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Capa PVC Cristal com manga, produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18627,11 +18447,7 @@
           <t>Capa PVC Cristal com manga GG, incolor.</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18723,11 +18539,7 @@
           <t>Capacete 800 Branco com carneira, um equipamento de segurança para uso em motocicletas.</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18771,11 +18583,7 @@
           <t>Capacete 800 na cor cinza com carneira.</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18819,11 +18627,7 @@
           <t>Capacete azul com carneira.</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18867,11 +18671,7 @@
           <t>Capacete CA 31469, um Equipamento de Proteção Individual (EPI) para segurança em ambientes de trabalho.</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18915,11 +18715,7 @@
           <t>Carneira para máscara de solda, um acessório essencial para proteção durante trabalhos de soldagem.</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -18963,11 +18759,7 @@
           <t>Carneira simples para capacete, um acessório de segurança para motociclistas.</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19011,11 +18803,7 @@
           <t>Cinto de ferramentas duplo da marca Worker, projetado para facilitar o transporte e organização de ferramentas.</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19251,11 +19039,7 @@
           <t>Colete refletivo LJ com 2 bolsos, tamanho G, da marca Worker.</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19299,11 +19083,7 @@
           <t>Colete refletivo LJ 4 com 4 bolsos, tamanho G, da marca Worker.</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19347,11 +19127,7 @@
           <t>Colete refletivo LJ 4 com 4 bolsos, tamanho GG, da marca Worker.</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19491,11 +19267,7 @@
           <t>Colete refletivo feito de poliéster, tamanho único, modelo LJ Fluor Worker.</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -19587,11 +19359,7 @@
           <t>Coturno de segurança da marca Dallas, tamanho 40, com fechamento em velcro e solado acolchoado.</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr">
         <is>
           <t>Não encontrado</t>

--- a/saida/produtos_enriquecidos_parte_4.xlsx
+++ b/saida/produtos_enriquecidos_parte_4.xlsx
@@ -19643,11 +19643,7 @@
           <t>Coturno de segurança acolchoado com velcro, cor preta, tamanho 42, da marca Dallas.</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20027,11 +20023,7 @@
           <t>Lente interna Titanium, um componente óptico para uso interno, provavelmente em câmeras ou dispositivos eletrônicos.</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20214,16 +20206,8 @@
           <t>MATERIAL DE SEGURANCA</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>Luva de vaqueta P7, um produto não encontrado na busca web.</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20315,11 +20299,7 @@
           <t>Luva tricotada preta pigmentada para mãos e dedos.</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20363,11 +20343,7 @@
           <t>Luva tricotada pigmentada para mãos e dedos.</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20411,11 +20387,7 @@
           <t>Manga de raspa, modelo Ref 950, vendida em pares.</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20459,11 +20431,7 @@
           <t>Máscara de solda ESAB Swarm A10, um equipamento de proteção para soldadores.</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20507,11 +20475,7 @@
           <t>Máscara de solda GUEPAR, um equipamento de proteção para soldadores.</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20555,11 +20519,7 @@
           <t>Máscara de solda Kala K20, um equipamento de proteção essencial para soldadores.</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20603,11 +20563,7 @@
           <t>Máscara de solda manual modelo 620, com escudo de proteção.</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20651,11 +20607,7 @@
           <t>Máscara de solda profissional da linha Titanium Control, oferecendo proteção avançada para soldadores.</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20795,11 +20747,7 @@
           <t>Óculos Adventure Incolor 140, modelo de óculos de proteção para atividades ao ar livre.</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20843,11 +20791,7 @@
           <t>Óculos de proteção com ampla visão, modelo Euro.</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20939,11 +20883,7 @@
           <t>Óculos incolor CA 34082, um equipamento de proteção individual (EPI) para segurança.</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -20987,11 +20927,7 @@
           <t>Óculos para macaqueiro modelo 120. Equipamento de proteção para uso em oficinas e indústrias.</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21179,11 +21115,7 @@
           <t>Óculos Sky Ambar, modelo desconhecido.</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21227,11 +21159,7 @@
           <t>Óculos Sky Fume, modelo desconhecido.</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21275,11 +21203,7 @@
           <t>Óculos Sky Incolor, modelo desconhecido.</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21323,11 +21247,7 @@
           <t>Óculos Summer Ambar, modelo desconhecido.</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21371,11 +21291,7 @@
           <t>Óculos Summer Fume, um modelo de óculos de sol com lentes fumê.</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21419,11 +21335,7 @@
           <t>Óculos Summer Incolor, modelo desconhecido.</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21467,11 +21379,7 @@
           <t>Óculos de sol da marca Rayban, modelo Summer.</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21563,11 +21471,7 @@
           <t>Protetor auricular plug, dispositivo utilizado para proteger os ouvidos de ruídos altos.</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21659,11 +21563,7 @@
           <t>Protetor facial modelo 158V na cor verde.</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21707,11 +21607,7 @@
           <t>Protetor facial CA 11442 da Carbografite, um equipamento de proteção individual (EPI) para segurança.</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21755,11 +21651,7 @@
           <t>Respirador dobrável PFF2-S com válvula, projetado para oferecer proteção respiratória.</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -21899,11 +21791,7 @@
           <t>Par de vidros redondos pretos, modelo N.6.</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -22667,11 +22555,7 @@
           <t>Canto Colonial Quimiplast (Externo), um produto de acabamento para construção.</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -26363,11 +26247,7 @@
           <t>Perfil U usinada de 10 polegadas com 2 almas, modelo EMP2.</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -26459,11 +26339,7 @@
           <t>Perfil U usinada de 12 polegadas na 1 alma, utilizado em construções metálicas e obras.</t>
         </is>
       </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -26507,11 +26383,7 @@
           <t>Perfil U usinada de 12 polegadas, na 1 alma, modelo EMP2.</t>
         </is>
       </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -27947,11 +27819,7 @@
           <t>Trelíca de laje H12 com 12 metros de comprimento.</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30299,11 +30167,7 @@
           <t>Esmerilhadeira da marca CAT, modelo DX31B, alimentada por bateria de 18V.</t>
         </is>
       </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30587,11 +30451,7 @@
           <t>Serra circular da marca CAT, modelo DX53B, alimentada por bateria de 18V.</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30635,11 +30495,7 @@
           <t>Serra tico tico da marca CAT, modelo DX51B, alimentada por bateria de 18V.</t>
         </is>
       </c>
-      <c r="G634" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G634" t="inlineStr"/>
       <c r="H634" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30683,11 +30539,7 @@
           <t>Combo de ferramentas elétricas GSR 120-LI e GDR 120-LI com maleta 2B.</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G635" t="inlineStr"/>
       <c r="H635" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30731,11 +30583,7 @@
           <t>O Denver Attiva 65 é um aparelho eletrônico, mas não foram encontradas informações detalhadas sobre suas características.</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>Não encontradas especificações técnicas.</t>
-        </is>
-      </c>
+      <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30779,11 +30627,7 @@
           <t>O Denver Toro Super 250 é um aparelho de som automotivo, conhecido por sua potência e qualidade sonora.</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G637" t="inlineStr"/>
       <c r="H637" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30827,11 +30671,7 @@
           <t>Trator Denver Tractore 200, um equipamento agrícola robusto e versátil.</t>
         </is>
       </c>
-      <c r="G638" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30870,16 +30710,8 @@
           <t>MAQUINAS</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G639" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
       <c r="H639" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -30923,11 +30755,7 @@
           <t>Desincrustador pneumático de agulhas, utilizado para limpeza e manutenção de equipamentos.</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31019,11 +30847,7 @@
           <t>Esmerilhadeira pneumática de 5 polegadas, utilizada para trabalhos de acabamento e corte em metais.</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31499,11 +31323,7 @@
           <t>Ferramenta multifuncional a bateria que realiza 7 funções diferentes.</t>
         </is>
       </c>
-      <c r="G652" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31595,11 +31415,7 @@
           <t>Furadeira Impac Bosch GSB 13 RE 127 V, uma ferramenta elétrica potente para diversos trabalhos de perfuração.</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31691,11 +31507,7 @@
           <t>Furadeira Impac Bosch GSB 16 RE 110 V, uma ferramenta elétrica para perfuração em diversos materiais.</t>
         </is>
       </c>
-      <c r="G656" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31787,11 +31599,7 @@
           <t>Furadeira Impac Bosch GSB 450 RE, 127V.</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G658" t="inlineStr"/>
       <c r="H658" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -31835,11 +31643,7 @@
           <t>Furadeira Impac Bosch GSB 550 RE 11A0, 127V.</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32027,11 +31831,7 @@
           <t>Furadeira Makita com maleta, 127V, modelo 1640KX1.</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32075,11 +31875,7 @@
           <t>Furadeira Makita com maleta, 220V, modelo HP 1640KX1.</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32123,11 +31919,7 @@
           <t>Furadeira Makita sem maleta, modelo 127V HP 1640KX2.</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G665" t="inlineStr"/>
       <c r="H665" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32171,11 +31963,7 @@
           <t>Furadeira Makita HP1640, 127V, sem maleta.</t>
         </is>
       </c>
-      <c r="G666" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G666" t="inlineStr"/>
       <c r="H666" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32267,11 +32055,7 @@
           <t>Inversor de solda MMA com função de corte plasma, modelo CUT-500 PRO, para uso em rede elétrica de 220V.</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G668" t="inlineStr"/>
       <c r="H668" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32315,11 +32099,7 @@
           <t>Kit de 4 peças de acessórios para motocompressor, conhecido como MAM.</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G669" t="inlineStr"/>
       <c r="H669" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32363,11 +32143,7 @@
           <t>Kit de 5 peças de acessórios para motocompressor, conhecido como MAM.</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32454,16 +32230,8 @@
           <t>MAQUINAS</t>
         </is>
       </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G672" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
       <c r="H672" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32507,11 +32275,7 @@
           <t>Inversora de solda Boxer 140 BV Touch150, um equipamento para soldagem com tecnologia inverter.</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G673" t="inlineStr"/>
       <c r="H673" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32555,11 +32319,7 @@
           <t>Inversora de solda Boxer 160, modelo BV Flama161.</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G674" t="inlineStr"/>
       <c r="H674" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32603,11 +32363,7 @@
           <t>Inversora de solda Boxer 200, modelo BV Flama201, equipamento para soldagem.</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G675" t="inlineStr"/>
       <c r="H675" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32651,11 +32407,7 @@
           <t>MAQ SOLDA KENDE INVER SS-PRO160 BIVOLT - Equipamento de solda inverter bivolt da marca Kende.</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G676" t="inlineStr"/>
       <c r="H676" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32699,11 +32451,7 @@
           <t>Maquineta de solda Kende, modelo inversor MIG sem gás para arame de 1kg.</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G677" t="inlineStr"/>
       <c r="H677" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32747,11 +32495,7 @@
           <t>Inversor de solda Kende 130D, modelo bivolt.</t>
         </is>
       </c>
-      <c r="G678" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G678" t="inlineStr"/>
       <c r="H678" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32795,11 +32539,7 @@
           <t>Inversor de solda Kende 130D bivolt, produto em mosturário.</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G679" t="inlineStr"/>
       <c r="H679" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32843,11 +32583,7 @@
           <t>Inversora de solda Kende Top 275X, 220V, modelo mostreúario.</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G680" t="inlineStr"/>
       <c r="H680" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32939,11 +32675,7 @@
           <t>Máquina de solda inversora manual Velocce Plus.</t>
         </is>
       </c>
-      <c r="G682" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G682" t="inlineStr"/>
       <c r="H682" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -32987,11 +32719,7 @@
           <t>Maquinário de solda TWI-140 da Terra Invers, bivolt 110/220V.</t>
         </is>
       </c>
-      <c r="G683" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -33035,11 +32763,7 @@
           <t>Máquina de solda TWI-180 Terra Invers bivolt, compatível com 110V e 220V.</t>
         </is>
       </c>
-      <c r="G684" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G684" t="inlineStr"/>
       <c r="H684" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -33083,11 +32807,7 @@
           <t>Maquineta de solda TWI-200 Terra Invers, operação em 220V.</t>
         </is>
       </c>
-      <c r="G685" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G685" t="inlineStr"/>
       <c r="H685" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -33179,11 +32899,7 @@
           <t>Máquina de solda DV Invers Manual Denver Mini, um equipamento compacto para soldagem.</t>
         </is>
       </c>
-      <c r="G687" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G687" t="inlineStr"/>
       <c r="H687" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34043,11 +33759,7 @@
           <t>Parafuso furador 1 batida da marca Wurth, modelo ABSR 12, para uso em aplicações de 12V.</t>
         </is>
       </c>
-      <c r="G705" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34091,11 +33803,7 @@
           <t>Parafusadeira / Furadeira Bosch GRS 1000 Smart 12V, um equipamento portátil e versátil para diversas aplicações de parafusar e furar.</t>
         </is>
       </c>
-      <c r="G706" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G706" t="inlineStr"/>
       <c r="H706" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34139,11 +33847,7 @@
           <t>Parafusadeira / furadeira Bosch GSR 180 com bateria bivolt 18V.</t>
         </is>
       </c>
-      <c r="G707" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G707" t="inlineStr"/>
       <c r="H707" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34187,11 +33891,7 @@
           <t>Parafusadeira a bateria com cortador de chapa da linha Titanium.</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34283,11 +33983,7 @@
           <t>Parafusadeira Bosch GSR 6-25 TE 220V, modelo profissional.</t>
         </is>
       </c>
-      <c r="G710" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G710" t="inlineStr"/>
       <c r="H710" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34331,11 +34027,7 @@
           <t>Parafusadeira Impacto Ranger 21V com 1 bateria e maleta.</t>
         </is>
       </c>
-      <c r="G711" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34379,11 +34071,7 @@
           <t>Parafusadeira Ranger 21V com 2 baterias e malinha de transporte.</t>
         </is>
       </c>
-      <c r="G712" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G712" t="inlineStr"/>
       <c r="H712" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34427,11 +34115,7 @@
           <t>Parafusadeira Ranger 12V com 1 bateria incluída.</t>
         </is>
       </c>
-      <c r="G713" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G713" t="inlineStr"/>
       <c r="H713" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34523,11 +34207,7 @@
           <t>Pistola de gesso FAI72N com regulagem, um dispositivo para aplicação precisa de gesso.</t>
         </is>
       </c>
-      <c r="G715" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -34619,11 +34299,7 @@
           <t>Pistola de pintura elétrica Vonder PEV 400, 127V.</t>
         </is>
       </c>
-      <c r="G717" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G717" t="inlineStr"/>
       <c r="H717" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35147,11 +34823,7 @@
           <t>Conjunto de solda oxi-acetileno Millennium completo, utilizado para soldagem e corte de metais.</t>
         </is>
       </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G728" t="inlineStr"/>
       <c r="H728" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35243,11 +34915,7 @@
           <t>O Denver Ultra Super Bivolt é um aparelho elétrico, mas informações detalhadas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G730" t="inlineStr"/>
       <c r="H730" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35291,11 +34959,7 @@
           <t>Inversor de solda Ottima Super, um equipamento para soldagem profissional.</t>
         </is>
       </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35339,11 +35003,7 @@
           <t>Inversor ESAB Bantam 3.2, modelo bivolt, utilizado para soldagem.</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G732" t="inlineStr"/>
       <c r="H732" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35387,11 +35047,7 @@
           <t>Inversor ESAB LHN 242I PLUS, um equipamento de solda avançado.</t>
         </is>
       </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G733" t="inlineStr"/>
       <c r="H733" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35435,11 +35091,7 @@
           <t>Inversora ESAB Bantam 2,50 bivolt, equipamento para soldagem.</t>
         </is>
       </c>
-      <c r="G734" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35531,11 +35183,7 @@
           <t>MAQ SOLDA AWT INVERS MM-120EP MONO 127V, um equipamento de solda inversora monofásico.</t>
         </is>
       </c>
-      <c r="G736" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G736" t="inlineStr"/>
       <c r="H736" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35579,11 +35227,7 @@
           <t>Maquinário de solda inversora MIG, modelo Forza Super M DW2-250-K.</t>
         </is>
       </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G737" t="inlineStr"/>
       <c r="H737" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35627,11 +35271,7 @@
           <t>Policorte de ferro da marca Ferrari, modelo F-12.</t>
         </is>
       </c>
-      <c r="G738" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G738" t="inlineStr"/>
       <c r="H738" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -35675,11 +35315,7 @@
           <t>Serra de esquadria Makita 127V, fabricada em alumínio.</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36347,11 +35983,7 @@
           <t>Inversor de solda HANDYARC 132I BIVOLT, um equipamento portátil para soldagem.</t>
         </is>
       </c>
-      <c r="G753" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36395,11 +36027,7 @@
           <t>Inversora de solda KSI 130A Bivolt da marca Kala, equipamento para soldagem.</t>
         </is>
       </c>
-      <c r="G754" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G754" t="inlineStr"/>
       <c r="H754" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36443,11 +36071,7 @@
           <t>Inversora de solda KSI 130A Bivolt da marca Kala, equipamento para soldagem.</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36491,11 +36115,7 @@
           <t>Maquinário de solda inversora manual da marca Agille, modelo Super DM4-160.</t>
         </is>
       </c>
-      <c r="G756" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36539,11 +36159,7 @@
           <t>Martelete combinado Makita HR2670, acompanha mala, possui 127V.</t>
         </is>
       </c>
-      <c r="G757" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36587,11 +36203,7 @@
           <t>Martelete combinado Makita com malta, modelo M8701P, voltado para trabalhos de construção e demolição.</t>
         </is>
       </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36635,11 +36247,7 @@
           <t>Martelete combinado Makita M8701P, acompanha mala, possui 220V.</t>
         </is>
       </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36683,11 +36291,7 @@
           <t>Paraf/furadeira 12V com maleta da marca Wesco, modelo WS2555K.</t>
         </is>
       </c>
-      <c r="G760" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36875,11 +36479,7 @@
           <t>Serra mármore Makita 4100NH 3ZX2 127V, acompanha 2 discos.</t>
         </is>
       </c>
-      <c r="G764" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -36923,11 +36523,7 @@
           <t>Serra mármore Makita 4100NH 3ZX2 127V, sem malta.</t>
         </is>
       </c>
-      <c r="G765" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37019,11 +36615,7 @@
           <t>Serra Rápida Makita 127 V M2401B, ideal para cortes em ferro.</t>
         </is>
       </c>
-      <c r="G767" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37211,11 +36803,7 @@
           <t>Kit Reforma Express 1, um conjunto de ferramentas e materiais para facilitar pequenas reformas e reparos domésticos.</t>
         </is>
       </c>
-      <c r="G771" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G771" t="inlineStr"/>
       <c r="H771" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37259,11 +36847,7 @@
           <t>Kit de reforma express para facilitar pequenos reparos e melhorias em casa.</t>
         </is>
       </c>
-      <c r="G772" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G772" t="inlineStr"/>
       <c r="H772" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37307,11 +36891,7 @@
           <t>Kit Reforma Express 3, um conjunto de ferramentas e materiais para facilitar pequenas reformas e reparos domésticos.</t>
         </is>
       </c>
-      <c r="G773" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -37974,16 +37554,8 @@
           <t>CALHA</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G787" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr"/>
       <c r="H787" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38022,16 +37594,8 @@
           <t>CALHA</t>
         </is>
       </c>
-      <c r="F788" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38070,16 +37634,8 @@
           <t>CALHA</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. A busca retornou um erro.</t>
-        </is>
-      </c>
-      <c r="G789" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38123,11 +37679,7 @@
           <t>Suposto suporte para calha J-40 reto, utilizado em instalações de calhas para drenagem de água.</t>
         </is>
       </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G790" t="inlineStr"/>
       <c r="H790" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38171,11 +37723,7 @@
           <t>Suposto suporte para calha J-40 torcido, utilizado em instalações de calhas e condutos.</t>
         </is>
       </c>
-      <c r="G791" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38219,11 +37767,7 @@
           <t>Suposto suporte para calha modelo Q-40 reto, mas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G792" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38267,11 +37811,7 @@
           <t>Suposto suporte para calha modelo Q-40 torcido, mas informações específicas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G793" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38315,11 +37855,7 @@
           <t>Tampa para calha J-40, lado direito.</t>
         </is>
       </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G794" t="inlineStr"/>
       <c r="H794" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38363,11 +37899,7 @@
           <t>Tampa para calha J-40, lado esquerdo.</t>
         </is>
       </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G795" t="inlineStr"/>
       <c r="H795" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -38411,11 +37943,7 @@
           <t>Tampa para calha Q-40, um acessório de vedação e proteção para sistemas de drenagem.</t>
         </is>
       </c>
-      <c r="G796" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -39035,11 +38563,7 @@
           <t>Cantoneira de dimensões 2 x 1/4, utilizada em aplicações de construção e acabamento.</t>
         </is>
       </c>
-      <c r="G809" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G809" t="inlineStr"/>
       <c r="H809" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -39083,11 +38607,7 @@
           <t>Cantoneira de dimensões 2 x 1/4, utilizada para reforço estrutural em construções e montagens.</t>
         </is>
       </c>
-      <c r="G810" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G810" t="inlineStr"/>
       <c r="H810" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -39131,11 +38651,7 @@
           <t>Cantoneira de dimensões 2 x 1/8, utilizada em aplicações de acabamento e reforço.</t>
         </is>
       </c>
-      <c r="G811" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G811" t="inlineStr"/>
       <c r="H811" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -40619,11 +40135,7 @@
           <t>Patamar caracol de 60cm, um produto cujas informações detalhadas não foram encontradas.</t>
         </is>
       </c>
-      <c r="G842" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G842" t="inlineStr"/>
       <c r="H842" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -40763,11 +40275,7 @@
           <t>PATAMAR CARACOL 80CM, um produto cujas informações não foram encontradas na busca web.</t>
         </is>
       </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G845" t="inlineStr"/>
       <c r="H845" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -41291,11 +40799,7 @@
           <t>Bobina pronta de 5 metros, modelo EMP2.</t>
         </is>
       </c>
-      <c r="G856" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G856" t="inlineStr"/>
       <c r="H856" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -41483,11 +40987,7 @@
           <t>Bobina vazia para impressão 3D.</t>
         </is>
       </c>
-      <c r="G860" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G860" t="inlineStr"/>
       <c r="H860" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -41627,11 +41127,7 @@
           <t>Chumbador bicomponente em ampola de 10mm, utilizado para fixação em obras e construção.</t>
         </is>
       </c>
-      <c r="G863" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G863" t="inlineStr"/>
       <c r="H863" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -41675,11 +41171,7 @@
           <t>Chumbador bicomponente em ampola de 16mm. Produto utilizado para fixação em construções.</t>
         </is>
       </c>
-      <c r="G864" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G864" t="inlineStr"/>
       <c r="H864" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -41819,11 +41311,7 @@
           <t>Poste galvanizado de 4 metros, modelo 18.</t>
         </is>
       </c>
-      <c r="G867" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G867" t="inlineStr"/>
       <c r="H867" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42011,11 +41499,7 @@
           <t>Guia para mola de porta de aço, utilizado para instalação e ajuste de molas em portas de aço.</t>
         </is>
       </c>
-      <c r="G871" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G871" t="inlineStr"/>
       <c r="H871" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42054,16 +41538,8 @@
           <t>MAT.PORTA DE ACO</t>
         </is>
       </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>Leque sem mancal da marca Bandeira. Produto não encontrado na web.</t>
-        </is>
-      </c>
-      <c r="G872" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr"/>
       <c r="H872" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42203,11 +41679,7 @@
           <t>Pedal para porta de aço, dispositivo utilizado para facilitar a abertura de portas pesadas ou de aço.</t>
         </is>
       </c>
-      <c r="G875" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G875" t="inlineStr"/>
       <c r="H875" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42299,11 +41771,7 @@
           <t>Chumbadouro PRISIONEIRO G2 1/2 X 160 para ampolas AQA.</t>
         </is>
       </c>
-      <c r="G877" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G877" t="inlineStr"/>
       <c r="H877" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42347,11 +41815,7 @@
           <t>Chumbadouro PRISIONEIRO G2 1/2 X 250 para ampolas AQA.</t>
         </is>
       </c>
-      <c r="G878" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G878" t="inlineStr"/>
       <c r="H878" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42731,11 +42195,7 @@
           <t>Trelíca estrutural promocional na cor vermelha.</t>
         </is>
       </c>
-      <c r="G886" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G886" t="inlineStr"/>
       <c r="H886" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42779,11 +42239,7 @@
           <t>Expositor para óculos de segurança, utilizado para organizar e apresentar óculos de proteção em lojas ou ambientes de trabalho.</t>
         </is>
       </c>
-      <c r="G887" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G887" t="inlineStr"/>
       <c r="H887" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42827,11 +42283,7 @@
           <t>Expositor químico balcão Kala, utilizado para exibir produtos químicos em balcões de lojas.</t>
         </is>
       </c>
-      <c r="G888" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G888" t="inlineStr"/>
       <c r="H888" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42875,11 +42327,7 @@
           <t>Scooter elétrica vermelha com chassi SH48V8002505120807.</t>
         </is>
       </c>
-      <c r="G889" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G889" t="inlineStr"/>
       <c r="H889" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42923,11 +42371,7 @@
           <t>O Algarismo 4 Cor Bronze é um item decorativo ou de sinalização, provavelmente usado em placas ou displays.</t>
         </is>
       </c>
-      <c r="G890" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G890" t="inlineStr"/>
       <c r="H890" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -42971,11 +42415,7 @@
           <t>Algarismo 8 de cor bronze. Parece ser um item decorativo ou numérico para uso em placas, fachadas ou displays.</t>
         </is>
       </c>
-      <c r="G891" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G891" t="inlineStr"/>
       <c r="H891" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43019,11 +42459,7 @@
           <t>Algarismo 9 cor bronze. Elemento decorativo ou numérico para identificação.</t>
         </is>
       </c>
-      <c r="G892" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G892" t="inlineStr"/>
       <c r="H892" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43062,16 +42498,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F893" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. Não há informações disponíveis sobre o Algarismo Alumínio N, 4 *.</t>
-        </is>
-      </c>
-      <c r="G893" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr"/>
       <c r="H893" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43115,11 +42543,7 @@
           <t>Algarismo de alumínio, modelo N, com 5 unidades.</t>
         </is>
       </c>
-      <c r="G894" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G894" t="inlineStr"/>
       <c r="H894" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43163,11 +42587,7 @@
           <t>Algarismo de alumínio, modelo N, com 6 unidades.</t>
         </is>
       </c>
-      <c r="G895" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G895" t="inlineStr"/>
       <c r="H895" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43206,16 +42626,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F896" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. Não há informações disponíveis para o Algarismo Alumínio N, 7 *.</t>
-        </is>
-      </c>
-      <c r="G896" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr"/>
       <c r="H896" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43307,11 +42719,7 @@
           <t>Algarismo de alumínio, modelo N, número 9.</t>
         </is>
       </c>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t>Não encontrada</t>
-        </is>
-      </c>
+      <c r="G898" t="inlineStr"/>
       <c r="H898" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43403,11 +42811,7 @@
           <t>Batente de borracha grande, utilizado para amortecer impactos e proteger superfícies.</t>
         </is>
       </c>
-      <c r="G900" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G900" t="inlineStr"/>
       <c r="H900" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43451,11 +42855,7 @@
           <t>Bucha CX N 12, embalagem com 50 unidades.</t>
         </is>
       </c>
-      <c r="G901" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G901" t="inlineStr"/>
       <c r="H901" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43547,11 +42947,7 @@
           <t>Cadeira Samambaia Grande Al, um móvel de design rústico e elegante.</t>
         </is>
       </c>
-      <c r="G903" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G903" t="inlineStr"/>
       <c r="H903" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43595,11 +42991,7 @@
           <t>Calça azul royal G, um modelo de calça masculina ou feminina na cor azul.</t>
         </is>
       </c>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G904" t="inlineStr"/>
       <c r="H904" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43643,11 +43035,7 @@
           <t>Calça azul royal tamanho GG.</t>
         </is>
       </c>
-      <c r="G905" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G905" t="inlineStr"/>
       <c r="H905" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43691,11 +43079,7 @@
           <t>Calça azul royal M.</t>
         </is>
       </c>
-      <c r="G906" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G906" t="inlineStr"/>
       <c r="H906" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43739,11 +43123,7 @@
           <t>Calça cinza chumbo tamanho G.</t>
         </is>
       </c>
-      <c r="G907" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G907" t="inlineStr"/>
       <c r="H907" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43787,11 +43167,7 @@
           <t>Calça cinza chumbo GG. Informações específicas não disponíveis.</t>
         </is>
       </c>
-      <c r="G908" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G908" t="inlineStr"/>
       <c r="H908" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43835,11 +43211,7 @@
           <t>Calça cinza chumbo tamanho M.</t>
         </is>
       </c>
-      <c r="G909" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G909" t="inlineStr"/>
       <c r="H909" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43883,11 +43255,7 @@
           <t>Camisa polo feminina na cor azul marinho, tamanho G.</t>
         </is>
       </c>
-      <c r="G910" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G910" t="inlineStr"/>
       <c r="H910" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43931,11 +43299,7 @@
           <t>Camisa Polo Feminina Azul Marinho tamanho M.</t>
         </is>
       </c>
-      <c r="G911" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G911" t="inlineStr"/>
       <c r="H911" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -43979,11 +43343,7 @@
           <t>Camisa polo feminina na cor azul marinho, tamanho P.</t>
         </is>
       </c>
-      <c r="G912" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G912" t="inlineStr"/>
       <c r="H912" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44075,11 +43435,7 @@
           <t>Camisa Polo Feminina Azul Marinho tamanho XG.</t>
         </is>
       </c>
-      <c r="G914" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G914" t="inlineStr"/>
       <c r="H914" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44123,11 +43479,7 @@
           <t>Camisa polo masculina na cor azul marinho, tamanho G.</t>
         </is>
       </c>
-      <c r="G915" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G915" t="inlineStr"/>
       <c r="H915" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44171,11 +43523,7 @@
           <t>Camisa polo masculina na cor azul marinho, tamanho GG.</t>
         </is>
       </c>
-      <c r="G916" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G916" t="inlineStr"/>
       <c r="H916" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44219,11 +43567,7 @@
           <t>Camisa polo masculina na cor azul marinho, tamanho M.</t>
         </is>
       </c>
-      <c r="G917" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G917" t="inlineStr"/>
       <c r="H917" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44267,11 +43611,7 @@
           <t>Camisa polo masculina na cor azul royal com uma listra da marca Ribana.</t>
         </is>
       </c>
-      <c r="G918" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G918" t="inlineStr"/>
       <c r="H918" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44363,11 +43703,7 @@
           <t>Camisa polo masculina azul royal da marca Ribana, com uma listra.</t>
         </is>
       </c>
-      <c r="G920" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G920" t="inlineStr"/>
       <c r="H920" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44411,11 +43747,7 @@
           <t>Camisa regata azul royal da marca G.</t>
         </is>
       </c>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G921" t="inlineStr"/>
       <c r="H921" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44459,11 +43791,7 @@
           <t>Camisa regata azul royal tamanho GG.</t>
         </is>
       </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G922" t="inlineStr"/>
       <c r="H922" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44507,11 +43835,7 @@
           <t>Camisa regata azul royal modelo M.</t>
         </is>
       </c>
-      <c r="G923" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G923" t="inlineStr"/>
       <c r="H923" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44555,11 +43879,7 @@
           <t>Camisa regata na cor cinza chumbo, tamanho G.</t>
         </is>
       </c>
-      <c r="G924" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G924" t="inlineStr"/>
       <c r="H924" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44603,11 +43923,7 @@
           <t>Camisa regata na cor cinza chumbo, modelo GG.</t>
         </is>
       </c>
-      <c r="G925" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G925" t="inlineStr"/>
       <c r="H925" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44651,11 +43967,7 @@
           <t>Camisa regata na cor cinza chumbo, tamanho M.</t>
         </is>
       </c>
-      <c r="G926" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G926" t="inlineStr"/>
       <c r="H926" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44699,11 +44011,7 @@
           <t>Camisa regata de cor cinza claro, tamanho G.</t>
         </is>
       </c>
-      <c r="G927" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G927" t="inlineStr"/>
       <c r="H927" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44747,11 +44055,7 @@
           <t>Camisa regata de cor cinza claro, tamanho M.</t>
         </is>
       </c>
-      <c r="G928" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G928" t="inlineStr"/>
       <c r="H928" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44795,11 +44099,7 @@
           <t>Camisa social feminina tamanho G.</t>
         </is>
       </c>
-      <c r="G929" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G929" t="inlineStr"/>
       <c r="H929" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44843,11 +44143,7 @@
           <t>Camisa social feminina tamanho M.</t>
         </is>
       </c>
-      <c r="G930" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G930" t="inlineStr"/>
       <c r="H930" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44891,11 +44187,7 @@
           <t>Camisa social feminina tamanho P.</t>
         </is>
       </c>
-      <c r="G931" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G931" t="inlineStr"/>
       <c r="H931" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44939,11 +44231,7 @@
           <t>Camisa social feminina PP, um modelo básico para uso no dia a dia ou em ambientes de trabalho.</t>
         </is>
       </c>
-      <c r="G932" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G932" t="inlineStr"/>
       <c r="H932" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44987,11 +44275,7 @@
           <t>Camisa social masculina azul marinho no tamanho GG.</t>
         </is>
       </c>
-      <c r="G933" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G933" t="inlineStr"/>
       <c r="H933" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45035,11 +44319,7 @@
           <t>Camisa social masculina tamanho G.</t>
         </is>
       </c>
-      <c r="G934" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G934" t="inlineStr"/>
       <c r="H934" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45083,11 +44363,7 @@
           <t>Camisa social masculina tamanho GG.</t>
         </is>
       </c>
-      <c r="G935" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G935" t="inlineStr"/>
       <c r="H935" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45131,11 +44407,7 @@
           <t>Camisa social masculina tamanho M.</t>
         </is>
       </c>
-      <c r="G936" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G936" t="inlineStr"/>
       <c r="H936" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45179,11 +44451,7 @@
           <t>Camisa social masculina tamanho P.</t>
         </is>
       </c>
-      <c r="G937" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G937" t="inlineStr"/>
       <c r="H937" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45371,11 +44639,7 @@
           <t>Não foi possível obter informações sobre o produto.</t>
         </is>
       </c>
-      <c r="G941" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G941" t="inlineStr"/>
       <c r="H941" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45467,11 +44731,7 @@
           <t>Combo Touch145 220V com leitor óptico OptiArc 70, provavelmente usado para demonstração em lojas (mostriário).</t>
         </is>
       </c>
-      <c r="G943" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G943" t="inlineStr"/>
       <c r="H943" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45515,11 +44775,7 @@
           <t>Disco de corte diamantado para uso em ferramentas de corte de materiais duros.</t>
         </is>
       </c>
-      <c r="G944" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G944" t="inlineStr"/>
       <c r="H944" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46283,11 +45539,7 @@
           <t>Lente externa Master Weld Vision, um equipamento de proteção ocular para soldagem.</t>
         </is>
       </c>
-      <c r="G960" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46331,11 +45583,7 @@
           <t>Letra de alumínio, provavelmente utilizada para sinalização ou decoração.</t>
         </is>
       </c>
-      <c r="G961" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G961" t="inlineStr"/>
       <c r="H961" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46422,16 +45670,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F963" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G963" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr"/>
       <c r="H963" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46470,16 +45710,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F964" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G964" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr"/>
       <c r="H964" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46566,16 +45798,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F966" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G966" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46614,16 +45838,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F967" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G967" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46662,16 +45878,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F968" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G968" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr"/>
       <c r="H968" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46710,16 +45918,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F969" t="inlineStr">
-        <is>
-          <t>Produto não encontrado. Não há informações disponíveis sobre a LETRA METAL D *.</t>
-        </is>
-      </c>
-      <c r="G969" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr"/>
       <c r="H969" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46758,16 +45958,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F970" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G970" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46854,16 +46046,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F972" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G972" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46902,16 +46086,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F973" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G973" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr"/>
       <c r="H973" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47147,11 +46323,7 @@
           <t>MACHO WW AC 3/16 * - Conector elétrico para aplicações específicas.</t>
         </is>
       </c>
-      <c r="G978" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G978" t="inlineStr"/>
       <c r="H978" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47190,16 +46362,8 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F979" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
-      <c r="G979" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr"/>
       <c r="H979" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47387,11 +46551,7 @@
           <t>MAQ SOLDA AWT MIG SEM GAS MIG 140EF BIVOLT, equipamento de solda MIG/MAG sem gás para uso profissional e amador.</t>
         </is>
       </c>
-      <c r="G983" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G983" t="inlineStr"/>
       <c r="H983" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47435,11 +46595,7 @@
           <t>Máscara de solda automática OptiArc 120, equipamento de proteção para soldagem.</t>
         </is>
       </c>
-      <c r="G984" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G984" t="inlineStr"/>
       <c r="H984" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47483,11 +46639,7 @@
           <t>Máscara de solda automática Spectra 180, um equipamento de proteção essencial para soldagem.</t>
         </is>
       </c>
-      <c r="G985" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G985" t="inlineStr"/>
       <c r="H985" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47531,11 +46683,7 @@
           <t>Máscara de solda automática Spectra 360, um equipamento de proteção para soldagem.</t>
         </is>
       </c>
-      <c r="G986" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G986" t="inlineStr"/>
       <c r="H986" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -48155,11 +47303,7 @@
           <t>Steel Deck 0,80 é um produto cujas informações não puderam ser obtidas devido a um erro na busca na web.</t>
         </is>
       </c>
-      <c r="G999" t="inlineStr">
-        <is>
-          <t>Não encontrado</t>
-        </is>
-      </c>
+      <c r="G999" t="inlineStr"/>
       <c r="H999" t="inlineStr">
         <is>
           <t>Não encontrado</t>

--- a/saida/produtos_enriquecidos_parte_4.xlsx
+++ b/saida/produtos_enriquecidos_parte_4.xlsx
@@ -5802,7 +5802,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>http://centrohierros.com/wp-content/uploads/2020/07/Tubo-Galvanizado-con-Rosca.jpg | https://www.ultrasteel.com.br/imagens/tubo-galvanizado-com-rosca/tubo-galvanizado-com-rosca.jpg | https://images.tcdn.com.br/img/img_prod/1308346/tubo_galvanizado_bs_1387_2_x_3_00_mm_x_6m_13323_1_228d57b4002a1503f942c4d075b09c8b.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6474,7 +6478,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://proyectoferretero.com/wp-content/uploads/2024/08/3050.jpg | https://ferreteria-laestrella.com/321-large_default/tubo-galvanizado-1-14-metro.jpg | https://www.ultrasteel.com.br/imagens/tubo-galvanizado-com-rosca/tubo-galvanizado-com-rosca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14386,7 +14394,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://66882.cdn.simplo7.net/static/66882/sku/tubos-redondo-tubo-industrial-redondo-76-20-mm-3--p-1686362177403.png | https://constructor31.vtexassets.com/arquivos/ids/166364-800-800?v=638182438356000000&amp;width=800&amp;height=800&amp;aspect=true | https://www.zotti.ind.br/fotos/1/1/z4170.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14434,7 +14446,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1791/1791781/produto/2526321209e9ec19e35.jpg | https://casamattos.fbitsstatic.net/img/p/tubo-preto-em-polietileno-3-4-x-2mm-c-100m-politubos-75108/261700-1.jpg?w=800&amp;h=800&amp;v=no-change&amp;qs=ignore | https://constructor31.vtexassets.com/arquivos/ids/166364-800-800?v=638182438356000000&amp;width=800&amp;height=800&amp;aspect=true</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14534,7 +14550,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_627083-MLB92687945209_092025-O.webp | https://cdn.leroymerlin.com.br/products/03_tubos_01_mt__redondo_3_4_19,05mm__chapa_18num_aco_metalon_1572696001_4438_600x600.jpg | https://cdn.awsli.com.br/800x800/233/233940/produto/52070704/84f46dac5e.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14582,7 +14602,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/2599/2599903/produto/247076439/tubo-preto-redondo-site-cpkfoivgeo.png | https://imperiodostubos.com.br/produtos/5857.jpg | https://www.zeusdobrasil.com.br/storage/images/cache/tubo-aco-carbono-preto-din-2440-nbr-5580m-6-metros-21-2-pol-7454-1024-0f088a3e.webp</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14678,7 +14702,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://compraco.com.br/cdn/shop/files/Fabricante_de_Tubos_de_A_o_Carbono.png?v=1743693254&amp;width=1946 | https://www.losadatubos.com.br/imagens/informacoes/tubo-preto-din-01.webp | https://www.zeusdobrasil.com.br/storage/images/cache/tubo-aco-carbono-preto-nbr-5580l-6-metros-1-pol-7409-1024-d753b8f8.webp</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -20050,7 +20078,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/sg-11134201-824i5-mdyrbctzkzk7cc | https://cdn.dlojavirtual.com/static1/101499/sku/epi-s-capacete-de-seguranca-c-carneiro-cinza-vonder-p-1713277633983.jpg | https://cdn.dlojavirtual.com/static1/101499/sku/epi-s-capacete-de-seguranca-c-carneiro-cinza-vonder-p-1713277633113.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -43118,7 +43150,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J832" t="inlineStr"/>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>https://coferpon.com.br/wp-content/uploads/2021/12/degrau-xadrez-reto-u.png | https://www.fortedoserralheiro.com.br/2117-product_zoom/degrau-xadrez-reto.jpg | https://acosales.com.br/wp-content/uploads/2024/09/DEGRAU-PATAMAR-XADREZ-ANTIDERRAPANTE.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -43166,7 +43202,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J833" t="inlineStr"/>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>https://acosales.com.br/wp-content/uploads/2024/09/DEGRAU-PATAMAR-XADREZ-ANTIDERRAPANTE.jpg | https://www.fortedoserralheiro.com.br/2117-product_zoom/degrau-xadrez-reto.jpg | https://http2.mlstatic.com/D_NQ_NP_843956-MLB86664517788_062025-O-degrau-60x25cm-em-z-chapa-xadrez-18-3175mmaco-carbono.webp</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -43214,7 +43254,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J834" t="inlineStr"/>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>https://acosales.com.br/wp-content/uploads/2024/09/DEGRAU-RETO-XADREZ.jpeg | https://acosales.com.br/wp-content/uploads/2024/09/DEGRAU-PATAMAR-XADREZ-ANTIDERRAPANTE.jpg | https://www.fortedoserralheiro.com.br/2117-product_zoom/degrau-xadrez-reto.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -43262,7 +43306,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J835" t="inlineStr"/>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>https://coferpon.com.br/wp-content/uploads/2021/12/degrau-xadrez-reto-u.png | https://www.fortedoserralheiro.com.br/2117-product_zoom/degrau-xadrez-reto.jpg | https://acosales.com.br/wp-content/uploads/2024/09/DEGRAU-PATAMAR-XADREZ-ANTIDERRAPANTE.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -43830,7 +43878,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J847" t="inlineStr"/>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>https://coferpon.com.br/wp-content/uploads/2021/12/degrau-xadrez-reto-u.png | https://www.ferronor.com.br/imagens/ferro-aco/degrau-patamar.jpg | http://www.target.com.br/thumb/cacheviewergenius/11177</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -43878,7 +43930,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J848" t="inlineStr"/>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>https://loja.mendesemendesferroeaco.com.br/image/cache/catalog/produtos-integracao/PRD00674-omie___patamar-para-escada-reto-xadrez-60x60cm__conv-600x600.jpg | https://i.ytimg.com/vi/HI6_1m0KFq8/maxresdefault.jpg | https://www.sirlenepedras.com.br/produtos/11.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -43974,7 +44030,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J850" t="inlineStr"/>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>https://carpintariarezende.com.br/wp-content/uploads/2019/08/patamar-de-madeira.jpg | https://imgv2-2-f.scribdassets.com/img/document/971702421/original/5e332b61fd/1?v=1 | https://images.kkeu.de/is/image/BEG/Escadas_e_andaimes/Escadotes/Patamar_dobrável_pdplarge-mrd--AA00945284FF-01.jpg?wid=1920&amp;hei=1920</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -44022,7 +44082,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J851" t="inlineStr"/>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>https://coferpon.com.br/wp-content/uploads/2021/12/degrau-xadrez-reto-u.png | https://loja.mendesemendesferroeaco.com.br/image/cache/catalog/produtos-integracao/PRD00677-omie___patamar-para-escada-reto-xadrez-80x80cm__conv-1000x1000.jpg | https://www.ferronor.com.br/imagens/ferro-aco/degrau-patamar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -44070,7 +44134,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J852" t="inlineStr"/>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>https://loja.mendesemendesferroeaco.com.br/image/cache/catalog/produtos-integracao/PRD00677-omie___patamar-para-escada-reto-xadrez-80x80cm__conv-1000x1000.jpg | https://coferpon.com.br/wp-content/uploads/2021/12/degrau-xadrez-reto-u.png | https://www.ferronor.com.br/imagens/ferro-aco/degrau-patamar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -44166,7 +44234,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J854" t="inlineStr"/>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://www.coppermetal.com.br/wp-content/uploads/2024/10/bobinas-de-aco.jpg | https://genesiseletricablog.com.br/wp-content/uploads/2025/09/fio-eletrico-em-bobina-de-carretel--1024x538.webp</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -44214,7 +44286,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J855" t="inlineStr"/>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://www.coppermetal.com.br/wp-content/uploads/2024/10/bobinas-de-aco-1536x662.jpg | https://www.alekvs.com/wp-content/uploads/2025/05/hot-rolled-steel-coil.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -44247,15 +44323,19 @@
           <t>Bobina pronta de 5 metros, modelo EMP2.</t>
         </is>
       </c>
-      <c r="G856" t="inlineStr"/>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Fabricada em aço de alta resistência, alta durabilidade, compatível com diversos modelos de portas de enrolar, reduz o esforço necessário para abrir/fechar a porta, essencial para o bom funcionamento da porta, ideal para sistemas automáticos e manuais.</t>
+        </is>
+      </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://acosales.com.br/produto/bobina-mola/</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>Não encontrado</t>
+          <t>https://pt.scribd.com/document/534979225/Manual-Porta-de-Enrolar</t>
         </is>
       </c>
       <c r="J856" t="inlineStr"/>
@@ -44306,7 +44386,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J857" t="inlineStr"/>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://cdn.avanteplus.com.br/stores/gasparferragens/image/263579-bobina-par9991.jpg | https://www.coppermetal.com.br/wp-content/uploads/2024/10/bobinas-de-aco-1536x662.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -44354,7 +44438,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J858" t="inlineStr"/>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>https://cdn.avanteplus.com.br/stores/gasparferragens/image/263579-bobina-par9991.jpg | https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://www.alekvs.com/wp-content/uploads/2025/05/hot-rolled-steel-coil.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -44402,7 +44490,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J859" t="inlineStr"/>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://cdn.avanteplus.com.br/stores/gasparferragens/image/263579-bobina-par9991.jpg | https://www.coppermetal.com.br/wp-content/uploads/2024/10/bobinas-de-aco.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -44446,7 +44538,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J860" t="inlineStr"/>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>https://jmwacos.com.br/wp-content/uploads/2024/03/Leno-170-_MFZ7428-1024x682.jpg | https://img.olx.com.br/images/93/934540445993407.jpg | https://cdn.avanteplus.com.br/stores/gasparferragens/image/263579-bobina-par9991.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -44494,7 +44590,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J861" t="inlineStr"/>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>http://www.calhasgomes.com.br/calhas/imagens/chapas-galvanizadas-24.jpg | https://acosbandeirantes.com/wp-content/uploads/2021/01/tiraraiada4.jpg | http://www.calhasgomes.com.br/calhas/imagens/chapa-galvanizada-24.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -44542,7 +44642,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J862" t="inlineStr"/>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1318890/chapa_galvanizada_26_1_20x3m_19207_1_a7fe03e42c1ee0d67fa93b5da2fb3a1c.jpg | https://images.tcdn.com.br/img/img_prod/1318890/chapa_galvanizada_26_1_20x3m_19207_3_e64bfdbce8c8e25bc69236f4afe74a93.jpg | https://images.tcdn.com.br/img/img_prod/1318890/chapa_galvanizada_26_1_20x3m_19207_2_cb6bf856c0991a1532930943573045a1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -44575,7 +44679,11 @@
           <t>Chumbador bicomponente em ampola de 10mm, utilizado para fixação em obras e construção.</t>
         </is>
       </c>
-      <c r="G863" t="inlineStr"/>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Diâmetro: 10mm, Tipo: Bicomponente, Embalagem: Ampola</t>
+        </is>
+      </c>
       <c r="H863" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44586,7 +44694,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J863" t="inlineStr"/>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_759806-MLB90542492558_082025-O.webp | https://http2.mlstatic.com/D_NQ_NP_938082-MLB83531702234_042025-O-kit-5-chumbador-quimico-ancora-ampola-aqa10-10mm-fixaco.webp | https://veppel.com.br/wp-content/uploads/2025/06/Chumbador-ampola-quimica-768x768.png</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -44630,7 +44742,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J864" t="inlineStr"/>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1709/1709002/produto/260097577/150w--7--ttyxj2hix1.jpg | https://down-br.img.susercontent.com/file/sg-11134201-23010-ay7px69f1tlv6f | https://veppel.com.br/wp-content/uploads/2025/06/Chumbador-ampola-quimica-768x768.png</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -44678,7 +44794,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J865" t="inlineStr"/>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>https://www.fortedoserralheiro.com.br/2840-product_zoom/emposta-galvanizada.jpg | https://www.fortedoserralheiro.com.br/2841-product_zoom/emposta-galvanizada.jpg | https://afabricadeportasdeaco.com.br/wp-content/uploads/2021/10/Portas-de-Aco-de-Enrolar-Foto-4-scaled.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -44726,7 +44846,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J866" t="inlineStr"/>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>https://www.fortedoserralheiro.com.br/2840-product_zoom/emposta-galvanizada.jpg | https://www.fortedoserralheiro.com.br/2841-product_zoom/emposta-galvanizada.jpg | http://www.cotanet.com.br/img/site/paginas/porta-de-aco-galvanizado.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -44759,7 +44883,11 @@
           <t>Poste galvanizado de 4 metros, modelo 18.</t>
         </is>
       </c>
-      <c r="G867" t="inlineStr"/>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>Comprimento: 4 metros, Material: Aço galvanizado</t>
+        </is>
+      </c>
       <c r="H867" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -44770,7 +44898,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J867" t="inlineStr"/>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>https://www.fortedoserralheiro.com.br/2840-product_zoom/emposta-galvanizada.jpg | https://www.fortedoserralheiro.com.br/2841-product_zoom/emposta-galvanizada.jpg | https://portadeenrolar.ingaportas.com.br/wp-content/uploads/2022/07/Porta-de-Aco-Galvanizada-Guaruportas-13.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -44866,7 +44998,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J869" t="inlineStr"/>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>https://afabricadeportasdeaco.com.br/wp-content/uploads/2021/10/Portas-de-Aco-de-Enrolar-Foto-4-scaled.jpg | http://www.sandre.com.br/images/produtos/catalogos/porta-de-aco-frente.jpg | https://i.ytimg.com/vi/iItHzxyQ90U/maxresdefault.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -44914,7 +45050,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J870" t="inlineStr"/>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_889103-MLB84241498865_042025-O-fita-lateral-para-porta-de-aco-25mm-5-metros-90-rebites.webp | https://http2.mlstatic.com/D_NQ_NP_774868-MLB78857074781_092024-O-fita-lateral-para-porta-de-aco-25mm-30-metros-300-rebites.webp | https://http2.mlstatic.com/D_NQ_NP_831665-MLB53670269355_022023-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -44958,7 +45098,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J871" t="inlineStr"/>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>https://www.somolas.com.br/blog/doutor/uploads/0/blog/2025/01/blog-mola-para-porta-de-a-ccedil-o-de-enrolar-guia-completo-dd52619fb6.png | https://http2.mlstatic.com/D_NQ_NP_662086-MLB75910370095_042024-O.webp | https://http2.mlstatic.com/D_NQ_NP_877225-MLB76197616854_052024-O-mola-para-porta-de-aco-45mm-3x45-1-14-rn-tolemat.webp</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -44986,7 +45130,11 @@
           <t>MAT.PORTA DE ACO</t>
         </is>
       </c>
-      <c r="F872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Leque sem mancal da marca Bandeira, um dispositivo utilizado para dissipar calor em sistemas elétricos.</t>
+        </is>
+      </c>
       <c r="G872" t="inlineStr"/>
       <c r="H872" t="inlineStr">
         <is>
@@ -44998,7 +45146,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J872" t="inlineStr"/>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>https://cdn.avanteplus.com.br/stores/gasparferragens/image/mancalpor.91532.161.jpg | https://montal.com.br/wp-content/uploads/2022/09/194-com-logo.jpg | https://montal.com.br/wp-content/uploads/2022/09/193-com-logo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -45046,7 +45198,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J873" t="inlineStr"/>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_953624-MLB73320826178_122023-O.webp | https://images.tcdn.com.br/img/img_prod/1239457/kit_04_mancal_tipo_oval_fl_206_eixo_30_mm_2791_1_7850d2698376cd47e4a1007ea26a872a.jpg | https://cdn.avanteplus.com.br/stores/gasparferragens/image/mancalpor.91532.161.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -45094,7 +45250,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J874" t="inlineStr"/>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>https://cdn.avanteplus.com.br/stores/gasparferragens/image/mancalpor.91532.161.jpg | https://http2.mlstatic.com/D_NQ_NP_780209-MLB79947470266_102024-O.webp | https://http2.mlstatic.com/D_NQ_NP_792619-MLB91920506604_092025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -45138,7 +45298,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J875" t="inlineStr"/>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/sg-11134201-7rdxc-mdtp8fdwndw9e1 | https://paraferro.com.br/loja/wp-content/uploads/2019/08/image293.jpg | http://www.tolemat.com.br/site/content/produtos/16-Pedal+para+porta+de+aço/default.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -45186,7 +45350,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J876" t="inlineStr"/>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>https://minasaco.com/wp-content/uploads/2023/02/CHAPA-ONDULADA-1.png | https://acosales.com.br/wp-content/uploads/2024/09/LAMBRI-ONDULADO.jpg | https://minasaco.com/wp-content/uploads/2023/02/CHAPA-LAMBRIL-2-1024x826.png</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -45219,7 +45387,11 @@
           <t>Chumbadouro PRISIONEIRO G2 1/2 X 160 para ampolas AQA.</t>
         </is>
       </c>
-      <c r="G877" t="inlineStr"/>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Diâmetro: 1/2 polegada, Comprimento: 160mm, Material: Inox químico</t>
+        </is>
+      </c>
       <c r="H877" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45230,7 +45402,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J877" t="inlineStr"/>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_679343-MLB74324896959_012024-O.webp | https://images.tcdn.com.br/img/img_prod/473368/chumbador_prisioneiro_parabolt_inox_quimico_1_2_x_160_ancora_4374_3_bebebb39173f26fb4ef7d590d8dda8db.jpg | https://http2.mlstatic.com/D_NQ_NP_992228-MLB91601954993_092025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -45263,7 +45439,11 @@
           <t>Chumbadouro PRISIONEIRO G2 1/2 X 250 para ampolas AQA.</t>
         </is>
       </c>
-      <c r="G878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Diâmetro: 1/2 polegada, Comprimento: 250mm, Material: Aço Inox, Tipo: Chumbador para ampolas AQA</t>
+        </is>
+      </c>
       <c r="H878" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45274,7 +45454,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J878" t="inlineStr"/>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_606679-MLB79374693688_092024-O.webp | https://http2.mlstatic.com/D_NQ_NP_761236-MLB84917197799_052025-O-kit-10-prisioneiros-inox-12-x-250mm-c-porcas-e-arruelas.webp | https://images.tcdn.com.br/img/img_prod/473368/chumbador_prisioneiro_parabolt_inox_quimico_1_2_x_135_ancora_2114_1_3890d001a1690e999e41ffa9460cdefa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -45322,7 +45506,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J879" t="inlineStr"/>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>https://ccp.vteximg.com.br/arquivos/ids/205832-1000-1000/prisioneiro-3-8-x-130-p-chumbador-quimico.jpg?v=636117172922800000 | https://www.andreoziacessorios.com.br/uploads/img/produtos/2812/produtos_fotos/d0737a971c86692a64c0dda3b0c86373.jpg | https://ccp.vtexassets.com/arquivos/ids/324246/haste-prisioneiro.png?v=638567491559930000</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -45370,7 +45558,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J880" t="inlineStr"/>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_613261-MLB77649276677_072024-O-haste-prisioneiro-58-x-190-mm-p-chumb-quimico-5-un-ancora.webp | https://http2.mlstatic.com/D_NQ_NP_906373-MLB90015684737_082025-O.webp | http://www.mecfix.com.br/imagens_db/avatar_67cb48121e144_CHUMBADOR_PRISIONEIRO_gd.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -45418,7 +45610,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J881" t="inlineStr"/>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>https://diferraco.com/site/wp-content/uploads/2022/05/trelicas.jpg | https://images.tcdn.com.br/img/img_prod/1051709/180_trelica_estrutural_para_telhado_133_1_42e029e466c453fc60309b73940c10c5.png | https://api.aecweb.com.br/cls/anuncios/pes_123709/1-gr-trelica-estrutural.webp</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -45466,7 +45662,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J882" t="inlineStr"/>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>https://img.olx.com.br/images/85/855561886557190.webp | https://diferraco.com/site/wp-content/uploads/2022/05/trelicas.jpg | https://static.wixstatic.com/media/b27a1e_cb941948a16642e694c48ac999f28fca~mv2.webp/v1/fit/w_500,h_500,q_90/file.webp</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -45514,7 +45714,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J883" t="inlineStr"/>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>https://img.olx.com.br/images/85/855561886557190.webp | https://static.wixstatic.com/media/b27a1e_cb941948a16642e694c48ac999f28fca~mv2.webp/v1/fit/w_500,h_500,q_90/file.webp | https://loja.mendesemendesferroeaco.com.br/image/cache/catalog/produtos-integracao/PRD00713-omie___trelica-h6-6-metros__conv-1000x1000.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -45610,7 +45814,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J885" t="inlineStr"/>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>https://img.olx.com.br/images/85/855561886557190.webp | https://inacioferros.com/wp-content/uploads/2023/11/Trelica-de-ferro-para-telhado.jpg | https://img.olx.com.br/images/61/614433690482832.webp</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -45654,7 +45862,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J886" t="inlineStr"/>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>https://www.estribosfumiyajau.com.br/doutor/uploads/2/produtos/2023/12/cover-trelicas-37e862a6d6.jpg | https://img.olx.com.br/images/85/855561886557190.webp | https://loja.mendesemendesferroeaco.com.br/image/cache/catalog/produtos-integracao/PRD00713-omie___trelica-h6-6-metros__conv-1000x1000.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -45698,7 +45910,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J887" t="inlineStr"/>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>https://www.southsafe.com.br/assets/img/produtos/expositor-p-oculos-linha-completa-1678390045.jpg | https://cdn.awsli.com.br/2500x2500/837/837475/produto/236049069/whatsapp-image-2023-10-03-at-11-48-52-e4pq90q48y.jpeg | https://images.tcdn.com.br/img/img_prod/1148844/expositor_de_poliestireno_para_5_oculos_000041_pr_preto_10555_7_390268e49eb9da2012268527d58e5b49.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -45742,7 +45958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J888" t="inlineStr"/>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>https://cdn.iset.io/assets/41026/produtos/1880/balcao-caixa-expositor-amapa.jpg | https://www.solucoesindustriais.com.br/images/produtos/imagens_10978/balcao-expositor-refrigerado_10978_55287_1532788282738_cover.jpg | https://www.tudoloja.com/25278-large_default/expositor-balcao-laterais-acrilico.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -45786,7 +46006,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J889" t="inlineStr"/>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/790521/scooter_eletrica_48v_1000w_duos_e_trek_vermelho_3317_1_346e04e6caefd4e18bb02ed35b6f171a.jpg | https://asturbr.com/wp-content/uploads/2025/12/Scooter-Eletrica-Astur-E-Plus-–-Vermelha-3.png | https://down-br.img.susercontent.com/file/br-11134207-7r98o-mdssc2we0ud565</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -45830,7 +46054,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J890" t="inlineStr"/>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/algarismo_4_numeral_125mm_ouro_escovado_200_4_1570452393_3798_600x600.jpg | https://cdn.awsli.com.br/2500x2500/2666/2666582/produto/326644051/8150863fa9314f5c256845f0d081a73d-3g6fjsvnmx.jpg | https://img.elo7.com.br/product/zoom/5331AFF/algarismo-residencial-acm-com-inox-personalizado-55x40-casa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -45863,7 +46091,11 @@
           <t>Algarismo 8 de cor bronze. Parece ser um item decorativo ou numérico para uso em placas, fachadas ou displays.</t>
         </is>
       </c>
-      <c r="G891" t="inlineStr"/>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>Numeral 8, 125mm, aço escovado, cor bronze.</t>
+        </is>
+      </c>
       <c r="H891" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45874,7 +46106,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J891" t="inlineStr"/>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/algarismo_8_numeral_125mm_aco_escovado_400_8_1570452424_754f_600x600.jpg | https://www.impeda.com.br/wp-content/uploads/2023/04/algarismos-de-aco-.jpg | https://tosel.vtexassets.com/arquivos/ids/191033-800-800?v=637991008396530000&amp;width=800&amp;height=800&amp;aspect=true</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -45946,8 +46182,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F893" t="inlineStr"/>
-      <c r="G893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Algarismo de alumínio polido, número 4, disponível em diferentes tamanhos.</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>Material: Alumínio polido. Tamanhos disponíveis: grande e médio.</t>
+        </is>
+      </c>
       <c r="H893" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -45958,7 +46202,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J893" t="inlineStr"/>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_polido_grande_numero_4_grelhasol_2553_1_07ce1c7f28aaf2673e89dbf6aee29915.jpeg | https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_medio_numero_4_grelhasol_2537_1_48b3940c9f3094a79556fee66f04daae.jpeg | https://images.tcdn.com.br/img/img_prod/920732/algarismo_para_casa_no_4_em_aluminio_atlas_27789_1_3f2f151c246bc03b2d96388da0db4489.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -45991,7 +46239,11 @@
           <t>Algarismo de alumínio, modelo N, com 5 unidades.</t>
         </is>
       </c>
-      <c r="G894" t="inlineStr"/>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>Material: Alumínio polido. Tamanho: Grande.</t>
+        </is>
+      </c>
       <c r="H894" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46002,7 +46254,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J894" t="inlineStr"/>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>https://tosel.vtexassets.com/arquivos/ids/190182-800-800?v=637990889681630000&amp;width=800&amp;height=800&amp;aspect=true | https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_polido_grande_numero_5_grelhasol_2555_1_2fe92abd7f8a7dc91eb0490f48e91202.jpeg | https://images.tcdn.com.br/img/img_prod/920732/algarismo_para_casa_no_5_em_aluminio_atlas_27791_1_8a061910765e6cd2bd5d2deecf434b65.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -46035,7 +46291,11 @@
           <t>Algarismo de alumínio, modelo N, com 6 unidades.</t>
         </is>
       </c>
-      <c r="G895" t="inlineStr"/>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>Material: Alumínio, Altura: 6 polegadas</t>
+        </is>
+      </c>
       <c r="H895" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46074,8 +46334,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F896" t="inlineStr"/>
-      <c r="G896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Algarismo de alumínio espelhado, número 7, com 25cm de altura. Ideal para decoração e sinalização.</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>Material: Alumínio espelhado; Altura: 25cm</t>
+        </is>
+      </c>
       <c r="H896" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46086,7 +46354,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J896" t="inlineStr"/>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1028926/algarismo_de_aluminio_espelhado_n07_25cm_decore_18547_1_6c339ca4e6e5fa7ec13f100cfe9655d3.jpg | https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_medio_numero_7_grelhasol_2543_1_0e299df3e4ee6e2a5df60049c0d9f1fa.jpeg | https://pedraopvc.vteximg.com.br/arquivos/ids/203259-1000-1000/algarismo-aluminio-luxo-polido-sete-15cm-prime-aluminio-1.0.jpg?v=638487818875970000</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -46134,7 +46406,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J897" t="inlineStr"/>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_medio_numero_8_grelhasol_2545_2_81de10b9171f2d151f36353eb9131891.png | https://images.tcdn.com.br/img/img_prod/1028926/algarismo_de_aluminio_espelhado_n08_25cm_decore_18393_1_4c10af7f61da09c8cb5d07dc2ba58986.jpg | https://images.tcdn.com.br/img/img_prod/1111274/algarismo_aluminio_polido_grande_numero_8_grelhasol_2561_1_3385fca7cc0921e34a913e02e5579896.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -46167,7 +46443,11 @@
           <t>Algarismo de alumínio, modelo N, número 9.</t>
         </is>
       </c>
-      <c r="G898" t="inlineStr"/>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>Material: Alumínio. Tamanho: Não especificado.</t>
+        </is>
+      </c>
       <c r="H898" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46178,7 +46458,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J898" t="inlineStr"/>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/920732/algarismo_p_casa_em_aluminio_n9_atlas_27799_1_09e430894b290616384c457ff1df2107_20240514163000.jpeg | https://images.tcdn.com.br/img/img_prod/1028926/algarismo_de_aluminio_espelhado_n09_25cm_decore_18559_1_775b2c362028b71f5afab0e1aaae911b.jpg | https://cdn.leroymerlin.com.br/products/algarismos_de_0_a_9_em_aluminio_polido_pequeno_14cm_1570582241_8ae4_600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -46226,7 +46510,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J899" t="inlineStr"/>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>https://cf.shopee.com.br/file/fc3e1f5bc15b9daa7373ec5355b53192 | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m84xnphburkhb1 | https://amgestoroutput.s3.amazonaws.com/saojudas/img_produtos/1713-09555213.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -46259,7 +46547,11 @@
           <t>Batente de borracha grande, utilizado para amortecer impactos e proteger superfícies.</t>
         </is>
       </c>
-      <c r="G900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>Dimensões: 195 x 80 x 80 mm</t>
+        </is>
+      </c>
       <c r="H900" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46270,7 +46562,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J900" t="inlineStr"/>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>https://polifer.pt/wp-content/uploads/2024/12/Batente-borracha-195-x80-x80-600x600.png | https://martfer.com.br/wp-content/uploads/2021/03/batente_de_borracha_grande_5887_1_20200924121143.jpg | https://http2.mlstatic.com/D_NQ_NP_753114-MLB75301421966_032024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -46303,7 +46599,11 @@
           <t>Bucha CX N 12, embalagem com 50 unidades.</t>
         </is>
       </c>
-      <c r="G901" t="inlineStr"/>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>Tamanho: 12mm, Quantidade: 50 unidades</t>
+        </is>
+      </c>
       <c r="H901" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46314,7 +46614,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J901" t="inlineStr"/>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_950464-MLB53687155052_022023-O.webp | https://cdn.leroymerlin.com.br/products/bucha_plastica_12mm_pct_c__50_bucha_plastica_12mm_pct_c_50_und_1572612542_85c2_600x600.jpg | https://d8vlg9z1oftyc.cloudfront.net/lojajfmaquinas/image/product/06fcc6191d84830b1911b980c483cdac20241002090459/850/nao-informado-pelo-erp-4_6744.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -46362,7 +46666,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J902" t="inlineStr"/>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-m3p8vlxwf0ol80 | https://globalcenter.agilecdn.com.br/335908.jpg | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m3p8vlxwgf919c</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -46406,7 +46714,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J903" t="inlineStr"/>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>https://elianadecora.com.br/wp-content/uploads/2025/05/CADEIRA-SAMAMBAIA-1024x981.jpg | https://images.tcdn.com.br/img/img_prod/1379902/cadeira_samambaia_197_8_a5d3d3b74c3d861654b9c3d7352ba1b6.jpg | https://elianadecora.com.br/wp-content/uploads/2025/05/Cadeira-Samambaia-1.png</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -46450,7 +46762,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J904" t="inlineStr"/>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1188426/calca_flare_azul_royal_95_2_68952e3bc745064c054f125c920a4259.jpg | https://images.tcdn.com.br/img/img_prod/921262/calca_perfeitinha_azul_royal_1543_3_88f40560633dc05ad6f1e599fb9a054a.jpg | https://privalia.vtexassets.com/arquivos/ids/276090102/17629424531362.jpg?v=638985538871470000</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -46494,7 +46810,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J905" t="inlineStr"/>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>https://cdn.cigame.com.br/produtos/44439/44439.jpg | https://unifranepi.com.br/wp-content/uploads/2023/02/510-CALCA-NR10-AZUL-ROYAL-COM-FAIXA-REFLETIVA-CA-36595-1024x1024.png | https://static.ecosweb.com.br/public/produtos/plus-size-feminino/calca-pantalona/calca-azul-royal-em-crepe-plano-acetinado_373050_600_1.webp</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -46527,7 +46847,11 @@
           <t>Calça azul royal M.</t>
         </is>
       </c>
-      <c r="G906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>Modelo: Flare ou Perfeitinha; Cor: Azul Royal; Material: Brim; Detalhes: Elástico total e refletivo.</t>
+        </is>
+      </c>
       <c r="H906" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -46538,7 +46862,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J906" t="inlineStr"/>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1188426/calca_flare_azul_royal_95_2_68952e3bc745064c054f125c920a4259.jpg | https://images.tcdn.com.br/img/img_prod/859641/calca_em_brim_azul_royal_com_elastico_total_e_refletivo_1089_1_6ecb2e6a697756b13cb651e55a76ab32.jpeg | https://images.tcdn.com.br/img/img_prod/921262/calca_perfeitinha_azul_royal_1543_3_88f40560633dc05ad6f1e599fb9a054a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -46582,7 +46910,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J907" t="inlineStr"/>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>https://cdn.sistemawbuy.com.br/arquivos/a909005735edae32b6bc126d5cb94ec0/produtos/66d0b1136c3c6/img_5014-66f3299b355ea.jpg | https://cdn.sistemawbuy.com.br/arquivos/a909005735edae32b6bc126d5cb94ec0/produtos/66d0b1136c3c6/img_5017-66f3299a0dfad.jpg | https://www.lotfitness.com.br/app-lotfitness/assets/images/dinamica/produto/359/cor_0/original/xlg036cz-calca-legging-poliamida-premium-com-bolso-cinza-chumbo-160924-7d7762.jpg.pagespeed.ic.juq4zUO0Yf.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -46626,7 +46958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J908" t="inlineStr"/>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/sg-11134201-7rd66-lwhrrg510lsz1b | https://59121.cdn.simplo7.net/static/59121/sku/feminino-calcas-calca-wide-leg-cinza-chumbo-f2907ch-p-1733159216402.jpg | https://59121.cdn.simplo7.net/static/59121/sku/feminino-calcas-calca-wide-leg-cinza-chumbo-f2907ch-p-1733159110442.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -46670,7 +47006,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J909" t="inlineStr"/>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>https://cdn.sistemawbuy.com.br/arquivos/a909005735edae32b6bc126d5cb94ec0/produtos/66d0b1136c3c6/img_5014-66f3299b355ea.jpg | https://www.youcom.com.br/_next/image?url=https://img.youcom.com.br/Custom/Content/Products/11/41/1141162_calca-pantalona-em-linho-101157023_l3_638665005795077714.webp&amp;w=750&amp;q=100 | https://59121.cdn.simplo7.net/static/59121/sku/feminino-calcas-calca-wide-leg-cinza-chumbo-f2907ch-p-1733159124986.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -46714,7 +47054,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J910" t="inlineStr"/>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>https://cdn.iset.io/assets/66687/produtos/21926/e419bf3bd869f17dceee3653cc943f546838b58dcda22.png | https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/1867965540038b1040d.jpg | https://static.netshoes.com.br/produtos/camisa-polo-lacoste-feminina/12/D66-8059-012/D66-8059-012_zoom1.jpg?ts=1695358901</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -46758,7 +47102,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J911" t="inlineStr"/>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>https://cdn.iset.io/assets/66687/produtos/21926/e419bf3bd869f17dceee3653cc943f546838b58dcda22.png | https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/1867965540038b1040d.jpg | https://static.netshoes.com.br/produtos/camisa-polo-lacoste-feminina/12/D66-8059-012/D66-8059-012_zoom1.jpg?ts=1695358901</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -46802,7 +47150,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J912" t="inlineStr"/>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>https://cdn.iset.io/assets/66687/produtos/21926/e419bf3bd869f17dceee3653cc943f546838b58dcda22.png | https://static.netshoes.com.br/produtos/camisa-polo-lacoste-feminina/12/D66-8059-012/D66-8059-012_zoom1.jpg?ts=1695358901 | https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/1867965540038b1040d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -46850,7 +47202,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J913" t="inlineStr"/>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>https://img.lojasrenner.com.br/item/928124431/original/3.jpg | https://citerol.vtexassets.com/arquivos/ids/171497/IMG_2980.jpg?v=638761051325900000 | https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/1867965540038b1040d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -46894,7 +47250,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J914" t="inlineStr"/>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>https://pintearte.com.br/wp-content/uploads/2024/10/03-51.png | https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/1867965540038b1040d.jpg | https://citerol.vtexassets.com/arquivos/ids/171497/IMG_2980.jpg?v=638761051325900000</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -46982,7 +47342,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J916" t="inlineStr"/>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1227799/camisa_polo_pura_raca_masc_azul_marinho_pr077727_9053_1_6c9921fad5a0cc542890c1629eda08cf.jpg | https://duplaface.ind.br/image/cache/catalog/002+MASCULINO/camisapoloazulmarinhoeditado-1000x600.jpg | https://cdn.awsli.com.br/2500x2500/425/425970/produto/376597503/whatsapp-image-2025-10-21-at-09-26-57-teuqr0xaf9.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -47118,7 +47482,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J919" t="inlineStr"/>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/186085895c7d948fd72.jpg | https://images.tcdn.com.br/img/img_prod/1023579/camisa_masculina_modelo_gola_polo_tecido_de_piquet_azul_royal_31063_2_e042651ca1be7e644986d7a0e2e6d39e.jpg | https://oneranch.com.br/wp-content/uploads/2021/07/POLO-AZUL-ROYAL.png</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -47162,7 +47530,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J920" t="inlineStr"/>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/1986/1986667/produto/186085895c7d948fd72.jpg | https://images.tcdn.com.br/img/img_prod/1023579/camisa_masculina_modelo_gola_polo_tecido_de_piquet_azul_royal_31063_2_e042651ca1be7e644986d7a0e2e6d39e.jpg | https://images.tcdn.com.br/img/img_prod/1023579/camisa_masculina_modelo_gola_polo_tecido_de_piquet_azul_royal_31063_1_93613be3ffd843c3b00798d21e90aa77.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -47206,7 +47578,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J921" t="inlineStr"/>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1151489/camisa_regata_dry_azul_royal_11606_1_a75d4e1b81a0ef08d858ad1e0946a56b.png | https://app.procatalogo.com.br/lbfitness/wp-content/uploads/sites/4305/2025/11/Imagem-do-WhatsApp-de-2025-11-13-às-18.22.33_e1f87983-600x900.webp?ver=202504151408 | https://cdn.awsli.com.br/2500x2500/2695/2695890/produto/302424717/imagem-do-whatsapp-de-2024-11-08---s--16-51-48_71bf1d2d-z41jwydxr0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -47250,7 +47626,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J922" t="inlineStr"/>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1151489/camisa_regata_dry_azul_royal_11606_1_a75d4e1b81a0ef08d858ad1e0946a56b.png | https://app.procatalogo.com.br/lbfitness/wp-content/uploads/sites/4305/2025/09/144-IMG_9765_09-04-2025-600x801.webp?ver=202504151408 | https://app.procatalogo.com.br/lbfitness/wp-content/uploads/sites/4305/2025/11/Imagem-do-WhatsApp-de-2025-11-13-às-18.22.33_e1f87983-600x900.webp?ver=202504151408</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -47294,7 +47674,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J923" t="inlineStr"/>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1151489/camisa_regata_dry_azul_royal_11606_1_a75d4e1b81a0ef08d858ad1e0946a56b.png | https://app.procatalogo.com.br/lbfitness/wp-content/uploads/sites/4305/2025/09/144-IMG_9765_09-04-2025-600x801.webp?ver=202504151408 | https://static.ecosweb.com.br/public/produtos/moda-masculina/regata/regata-masculina-azul-royal_361057_600_1.webp</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -47338,7 +47722,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J924" t="inlineStr"/>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/2749/2749820/produto/386222056/801-chb-frente-qcaghnxqmi.jpg | https://torratorra.vteximg.com.br/arquivos/ids/2042190/22111000189060cinzaescuro1.jpg?v=638742669013900000 | https://cdn.awsli.com.br/2500x2500/2749/2749820/produto/387170470/kt3-801chb-8iuvnxvrm8.png</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -47382,7 +47770,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J925" t="inlineStr"/>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/2749/2749820/produto/386222056/801-chb-perfil-4bipa2059i.jpg | https://cdn.awsli.com.br/2500x2500/2749/2749820/produto/386222056/801-chb-frente-qcaghnxqmi.jpg | https://imagedelivery.net/Cd5P8I1FT0Acf2nRDHzlLA/ee0abce7-9830-4a38-8e8f-3a4e0c8e1600/public</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -47470,7 +47862,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J927" t="inlineStr"/>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/873120/camiseta_regata_basica_lisa_cinza_claro_1553_1_859465a1accd856fdbd26d1f4fa06fd3.jpg | https://images.tcdn.com.br/img/img_prod/873120/camiseta_regata_basica_lisa_cinza_claro_1553_1_b1956a19cb3fc2aeae6e130c47cf28d6.jpg | https://cdnmidias.s3.amazonaws.com/tedcamisas.com.br/wp-content/uploads/2025/11/13132238/8753-Cinza-Claro-CM.png</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -47514,7 +47910,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J928" t="inlineStr"/>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/873120/camiseta_regata_basica_lisa_cinza_claro_1553_1_859465a1accd856fdbd26d1f4fa06fd3.jpg | https://images.tcdn.com.br/img/img_prod/873120/camiseta_regata_basica_lisa_cinza_claro_1553_1_b1956a19cb3fc2aeae6e130c47cf28d6.jpg | https://cdnmidias.s3.amazonaws.com/tedcamisas.com.br/wp-content/uploads/2025/11/13132238/8753-Cinza-Claro-CM.png</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -47558,7 +47958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J929" t="inlineStr"/>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/2500x2500/2499/2499806/produto/369846756/dsc_0214-92fbhezbgb.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-azul-aurora-chambray-p-1739209819862.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-curta-ultra-tech-azul-marinho-p-1737742005439.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -47602,7 +48006,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J930" t="inlineStr"/>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-ultra-tech-branca-p-1738160599794.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-azul-ibiza-p-1740655599525.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-ultra-tech-branca-p-1738160604148.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -47646,7 +48054,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J931" t="inlineStr"/>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-ultra-tech-branca-p-1738160599794.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-curta-ultra-tech-azul-marinho-p-1738161358667.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-curta-maquinetada-nome-p-1691592931740.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -47690,7 +48102,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J932" t="inlineStr"/>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>https://gmmoldes.com/wp-content/uploads/2025/01/CAMISA-SOCIAL-FEMININA-800x800.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-camisa-feminina-social-manga-longa-cinza-ibiza-p-1681236525761.jpg | https://58532.cdn.simplo7.net/static/58532/sku/feminino-kit-3-3-camisas-femininas-sociais-manga-longa-p-1738866761958.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -47723,7 +48139,11 @@
           <t>Camisa social masculina azul marinho no tamanho GG.</t>
         </is>
       </c>
-      <c r="G933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>Modelo: Manga longa, tecido poplin, cor azul marinho, tamanho GG.</t>
+        </is>
+      </c>
       <c r="H933" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -47734,7 +48154,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J933" t="inlineStr"/>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1023579/camisa_masculina_social_manga_longa_tecido_poplin_azul_marinho_31069_2_f348e366069b5b7dbddd6f22acdcbeb2.jpg | https://click.copapel.com.br/images/produtos/A03121.jpg | https://down-br.img.susercontent.com/file/sg-11134201-7rcd4-lteaj4i0rd4jde</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -47778,7 +48202,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J934" t="inlineStr"/>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-ls3cq4ib3yuzf7 | https://down-br.img.susercontent.com/file/sg-11134201-23020-pi16ysnif1nvd1 | https://58532.cdn.simplo7.net/static/58532/sku/masculino-camisa-masculina-social-slim-fit-manga-longa-2266-009--p-1662748836107.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -47822,7 +48250,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J935" t="inlineStr"/>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-81ztc-mjec9ebghybq75 | https://down-br.img.susercontent.com/file/br-11134207-7r98o-ls3cq4ib3yuzf7 | https://down-br.img.susercontent.com/file/br-11134207-81zu9-ml5qbklhjhfr88</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -47866,7 +48298,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J936" t="inlineStr"/>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>https://alternativauniforme.com.br/wp-content/uploads/2023/06/IMG_0920-768x1024.jpg | https://images.tcdn.com.br/img/img_prod/1131074/camisa_masculina_social_m_l_listras_2507_1_d4a411a5f80f83f37b7b571ade2d6f9c_20250805141526.jpg | https://cdn.awsli.com.br/2500x2500/2499/2499806/produto/256961384/img_9923-yn43c6twb7.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -47910,7 +48346,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J937" t="inlineStr"/>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>https://58532.cdn.simplo7.net/static/58532/sku/masculino-camisa-masculina-social-tradicional-manga-longa-marinho--p-1666359731188.jpg | http://lojaviego.com.br/cdn/shop/files/Camisa_Social_Branca_Masculina_Slim_Fit_Zone_1__1_11zon.webp?v=1717789296 | https://58532.cdn.simplo7.net/static/58532/sku/masculino-camisa-masculina-social-tradicional-manga-curta-caqui--p-1666358704148.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -47958,7 +48398,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J938" t="inlineStr"/>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>https://gmmoldes.com/wp-content/uploads/2023/07/MODELO-Camisa-Social-Masculina-Manga-Longa-PP-ao-GG.jpg | https://i.pinimg.com/736x/da/04/2b/da042b2029024f45f12325e543552037.jpg | https://uniforuze.com.br/wp-content/uploads/2023/04/RASCUNHO-45-scaled.png</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -48006,7 +48450,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J939" t="inlineStr"/>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-lwvggmzsq5jmd2 | https://a-static.mlcdn.com.br/undefinedxundefined/10-cantoneiras-l-em-pvc-20mm-x-20mm-x-15mm-x-30-metros-para-acabamentos-e-protecao-perfimax/lagosvariedades/001009947/4f7ac68c7699bf46119c7e25c7b36d33.jpeg | https://http2.mlstatic.com/D_NQ_NP_935980-MLB75016318334_032024-O-15-cantoneiras-l-pvc-20x20x15mmx-30mts-proteco-acabamento.webp</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -48054,7 +48502,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J940" t="inlineStr"/>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_877550-MLB54970454114_042023-O-cavalete-andaime-de-aco-100x120cm-capacidade-ate-200kg-2unid.webp | https://img.olx.com.br/images/97/977601494906950.jpg | https://a-static.mlcdn.com.br/470x352/cavalete-andaime-hayner-120-l-x-100-a-br/rcdeletrica2/10428070/67a45bea09e203e235221812506d91d1.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -48146,7 +48598,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J942" t="inlineStr"/>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>https://acoexpressba.com.br/assets/images/product/chapa_preta.jpg | https://portosulcomercial.com.br/fotos/1/339/Chapa-Preta-1.jpg | https://casaserralheiro.com.br/wp-content/uploads/2020/12/Casa-do-Serralheiro-Produtos-Chapas-Chapa-de-Aco-Preta-3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -48190,7 +48646,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J943" t="inlineStr"/>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_860848-MLB77440271592_072024-O-combo-touch-145-220v-optiarc-70-luva-soldador-boxer.webp | https://cdn.awsli.com.br/2500x2500/1845/1845490/produto/256082339b83b196037.jpg | https://down-br.img.susercontent.com/file/br-11134207-7r98o-lz91r3vqch3paf</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -48223,7 +48683,11 @@
           <t>Disco de corte diamantado para uso em ferramentas de corte de materiais duros.</t>
         </is>
       </c>
-      <c r="G944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>Diâmetro: 180mm, Segmentado, Material: Diamante</t>
+        </is>
+      </c>
       <c r="H944" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -48234,7 +48698,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J944" t="inlineStr"/>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1331559/kit_2_unid_disco_de_corte_diamantado_pyramid_maquitao_segmentado_180mm_2463_1_84d3a58cbec5e35737b9a88cb4dc7a74.jpg | https://img.lojadomecanico.com.br/IMAGENS/37/432/90078/Disco-de-Corte-Diamantado-Continuo-de-11-starrett-ddc110-1.JPG | https://img.lojadomecanico.com.br/IMAGENS/46/448/154560/1609178266948.JPG</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -48282,7 +48750,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J945" t="inlineStr"/>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>https://protendi.com.br/wp-content/uploads/2020/02/DISCO-DE-CORTE-METAL-4-D-19928-MAKITA.jpg | https://carrefourbr.vtexassets.com/arquivos/ids/8817656/29768854667294.jpg?v=637360490533970000 | https://http2.mlstatic.com/D_NQ_NP_770058-MLM79429266276_092024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -48330,7 +48802,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J946" t="inlineStr"/>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/608404/disco_de_corte_p_inox_115x1_0x22_2mm_standard_norton_34933_1_061cc3fe2aab4b48a3c55a368d4cc96d.jpg | https://http2.mlstatic.com/D_NQ_NP_857405-MLB94142751661_102025-O.webp | https://http2.mlstatic.com/D_NQ_NP_881168-MLA93195843139_092025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -48378,7 +48854,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J947" t="inlineStr"/>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>https://images-americanas.b2w.io/produtos/54064282/imagens/disco-corsistrip-superclean-ceramico-vermelho-grosso-diametro-115mm-furo-22mm-made-in-italy/54064281_1_xlarge.jpg | https://cdn.awsli.com.br/800x800/2696/2696181/produto/337185640/11129-x8xlbbh78f.jpg | https://galzer.com.br/wp-content/uploads/2025/05/115mm-disco_DISCOS-DE-ACABAMENTO-GROSSO_Frente.webp</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -48426,7 +48906,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J948" t="inlineStr"/>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>https://product-hub-prd.madeiramadeira.com.br/619692825/images/1287b71a-d383-45ad-82fd-3f84d001dd6a9e93914017492740dobradica1.jpg | https://down-br.img.susercontent.com/file/br-11134201-23010-wvdiafj1xnmv10 | https://orcamentor.com/media/insumos/11447.png</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -48474,7 +48958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J949" t="inlineStr"/>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>https://static.comercialapoio.com.br/public/apoioforros/imagens/produtos/emenda-h-rigida-6m-branca-637be6f2b8b54.jpg | https://static.comercialapoio.com.br/public/apoioforros/imagens/produtos/emenda-h-rigida-6m-branca-637be6f1cbd15.jpg | https://cdn.awsli.com.br/800x800/2685/2685391/produto/272477329/emenda-cinza-v6u3dtwped.png</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -48522,7 +49010,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J950" t="inlineStr"/>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>https://img.elo7.com.br/product/zoom/573C4BF/pinha-31cm.jpg | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_07_macica_em_ferro_fundido_1770_1_eed45c2078cabc627b1746ac5069b635.png | https://images.tcdn.com.br/img/img_prod/148301/pinha_no_07_macica_em_ferro_fundido_1770_2_4028fbee45fed2322059784356674ba1.png</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -48570,7 +49062,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J951" t="inlineStr"/>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/forro_pvc_frisado_7mm_barra_com_3_metros_branco_plasbil_6311_1_f9e1571fc373ab7327221ce386f9d92d.png | https://cdn.entrypoint.directory/assets/60194/produtos/346/95f57e033ecc9491a9d722113133b57e626afa26c256d.png | https://www.forroarte.com.br/imagens/informacoes/forro-pvc-frisado-preco-01.webp</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -48618,7 +49114,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J952" t="inlineStr"/>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/forro_pvc_frisado_7mm_barra_com_4_metros_branco_plasbil_6313_1_6b24f50071997d4726f98758ffa560af.png | https://www.forroarte.com.br/imagens/informacoes/forro-pvc-frisado-preco-01.webp | https://cdn.entrypoint.directory/assets/60194/produtos/347/8f51f66feadaecd9e868325d548f1e34626b0278c0eb6.png</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -48666,7 +49166,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J953" t="inlineStr"/>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/forro_pvc_frisado_7mm_barra_com_5_metros_branco_plasbil_6317_1_6b24f50071997d4726f98758ffa560af.png | https://nacruzeiro.com.br/wp-content/uploads/2022/05/Design-sem-nome-2022-05-12T095055.200-1-600x600.png | https://cdn.entrypoint.directory/assets/60194/produtos/346/95f57e033ecc9491a9d722113133b57e626afa26c256d.png</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -48714,7 +49218,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J954" t="inlineStr"/>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1111274/forro_pvc_frisado_7mm_barra_com_6_metros_branco_plasbil_6319_1_f9e1571fc373ab7327221ce386f9d92d.png | https://static3.tcdn.com.br/img/img_prod/767420/forro_eplast_pvc_frisado_6m_9507_1_7b5ae9d1cdf5297c3a09c0a2ebdbf4ea_20210406143321.jpg | https://casanur.com.br/media/catalog/product/cache/9/small_image/420x/602f0fa2c1f0d1ba5e241f914e856ff9/h/t/https___images.madeiramadeira.com.br_product_images_64640468-rodaforro-pvc-premium-branco-6m-plasbil89932-803-1-600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -48858,7 +49366,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J957" t="inlineStr"/>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_769976-MLB90163663424_082025-O-grampo-em-u-galvanizado-eletrolitico-1x516-i-10-un.webp | https://eletrotrafo.vteximg.com.br/arquivos/ids/169254-700-700/76870001-2-03.jpg?v=639053922277770000 | https://catalogo.fixagold.com.br/wp-content/uploads/2025/03/3.png</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -48954,7 +49466,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J959" t="inlineStr"/>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/843883/jaleco_manga_longa_acinturado_em_gabardine_57_2_e9920ff11be8a54dce483a9c8b51b1f3.jpg | https://down-br.img.susercontent.com/file/br-11134207-7r98o-ma8d1nsp0yba40 | https://images-americanas.b2w.io/produtos/3657122387/imagens/533-jaleco-masculino-manga-longa-com-botao-embutido/3657122387_1_xlarge.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -48998,7 +49514,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J960" t="inlineStr"/>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_620579-MLB31154569782_062019-O.webp | https://http2.mlstatic.com/D_NQ_NP_791302-MLB75867349123_042024-O-kit-com-5-lentes-externa-de-proteco-118x97mm-weld-vision.webp | https://alusolda.com.br/wp-content/uploads/2020/08/lente-externa-mascara-de-solda-1-1-800x800.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -49042,7 +49562,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J961" t="inlineStr"/>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>https://nibe.mx/wp-content/uploads/2025/06/V-3131.jpg | https://anunciosdealuminio.com/wp-content/uploads/2022/05/Letras-de-Aluminio-7.jpg | https://new.avanceytec.com.mx/img-nueva-generacion/materiales/laminas/rollo-aluminio-anonizado/laminas_de_aluminio_anodizado.webp</t>
+        </is>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -49090,7 +49614,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J962" t="inlineStr"/>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>https://www.tintacon.com.br/uploads/tintacon/produtos_imagens/LETRA-B-ESPECIAL15904387701009229078.png | https://down-br.img.susercontent.com/file/1c0edd45a34605197ae4de91b7be353c | https://product-hub-prd.madeiramadeira.com.br/545869134/images/e1c902a9-4d72-4288-9262-d21919af559adencialaluminiobroperplast.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -49118,8 +49646,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F963" t="inlineStr"/>
-      <c r="G963" t="inlineStr"/>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Letra de alumínio espelhado, modelo C, com altura de 9.5 cm. Ideal para decoração e sinalização.</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>Altura: 9.5 cm, Material: Alumínio espelhado</t>
+        </is>
+      </c>
       <c r="H963" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49130,7 +49666,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J963" t="inlineStr"/>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_NQ_NP_675598-MLM49132686978_022022-W.jpg | https://http2.mlstatic.com/D_NQ_NP_859151-MLU76160168029_052024-O.webp | https://images-americanas.b2w.io/produtos/4325587313/imagens/letra-aluminio-espelhado-c-9-5cm-57/4325587313_1_xlarge.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -49158,7 +49698,11 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F964" t="inlineStr"/>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Letra de alumínio, geralmente utilizada para sinalização e identificação em estabelecimentos comerciais.</t>
+        </is>
+      </c>
       <c r="G964" t="inlineStr"/>
       <c r="H964" t="inlineStr">
         <is>
@@ -49170,7 +49714,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J964" t="inlineStr"/>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>https://anunciosdealuminio.com/wp-content/uploads/2022/05/Letras-de-Aluminio-7.jpg | https://emplaca.ind.br/images/speasyimagegallery/albums/29/images/letras-alumnio-fundido-emplaca-01-006_x_thumb.jpg | https://abcmaior.com.br/produto/letra-em-aluminio-altura-35mm-e-relevo-5mm-modelo-comercial/512bdaf3432bb2a1459971e1cae569f2-2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -49218,7 +49766,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J965" t="inlineStr"/>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>https://www.tintacon.com.br/uploads/tintacon/produtos_imagens/LETRA-F-ESPECIAL15904388591002658721.png | https://www.tintacon.com.br/uploads/tintacon/produtos_imagens/Letra-Colonial-F---11-CM15899830482061167338.png | https://es.kdmfab.com/wp-content/uploads/2022/04/figure-3-cast-aluminum-letter.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -49246,8 +49798,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F966" t="inlineStr"/>
-      <c r="G966" t="inlineStr"/>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Letra de alumínio S, utilizada para sinalização e decoração.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>Material: Alumínio; Formato: Letra S; Aplicação: Sinalização, decoração.</t>
+        </is>
+      </c>
       <c r="H966" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49258,7 +49818,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J966" t="inlineStr"/>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>https://new.avanceytec.com.mx/img-nueva-generacion/materiales/laminas/rollo-aluminio-anonizado/laminas_de_aluminio_anodizado.webp | https://anunciosdealuminio.com/wp-content/uploads/2022/05/Letras-de-Aluminio-7.jpg | https://decoratumundo.com/wp-content/uploads/2022/12/0703-LETRAS-ALUMINIO-SANDWICH-8a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -49286,7 +49850,11 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F967" t="inlineStr"/>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Letra de alumínio, provavelmente usada para sinalização ou decoração.</t>
+        </is>
+      </c>
       <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
@@ -49298,7 +49866,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J967" t="inlineStr"/>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgAP0l7e9RP9csiTQAfOEu57q2X9qi1aBNu0UdHqPurWKLgP5pyHMWtPLc4io-pMA8Bm0riLuAEm0DNC88E95PCqJQlhG6PoRh8RE-HA_WAtJOw8PSlLyq4SHcENxiqadKgeI_IZOJ2GNrN/s1600/aluminium-alfabeto-t.png | https://anunciosdealuminio.com/wp-content/uploads/2022/05/Letras-de-Aluminio-7.jpg | https://laesquinadelherrero.ar/wp-content/uploads/2025/08/13022.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -49366,8 +49938,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="inlineStr"/>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Letra metálica adesiva em formato de 'D', disponível em diferentes tamanhos.</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>Material: Metal; Tipo: Adesivo; Tamanho: 80mm, 145mm</t>
+        </is>
+      </c>
       <c r="H969" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49378,7 +49958,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J969" t="inlineStr"/>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>https://www.fermoplast.com.br/app/assets/images/dinamica/produto/345/cor_0/aml-d-145mm-letra-d-220318-a5e750.jpg | https://www.fermoplast.com.br/app/assets/images/dinamica/produto/345/cor_0/aml-d-145mm-letra-d-220318-ada25f.jpg | https://www.bricopor.com/11599-medium_default/letra-metal-adesivo-80mm-d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -49406,7 +49990,11 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F970" t="inlineStr"/>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Letra metálica 'F', geralmente usada para decoração, sinalização ou design gráfico.</t>
+        </is>
+      </c>
       <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
@@ -49418,7 +50006,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J970" t="inlineStr"/>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>https://www.tintacon.com.br/uploads/tintacon/produtos_imagens/LETRA-F-ESPECIAL15904388591002658721.png | https://img.freepik.com/fotos-premium/alfabeto-de-metal-f-simbolo-para-web-ou-escrita-renderizacao-3d-letra-de-fonte-metalica-abc_682859-1508.jpg?w=2000 | https://img.freepik.com/fotos-premium/letra-metalica-f-3d-renderizacao-cromada-prata-alfabeto-fonte-letra-simbolo_1298779-7963.jpg?w=2000</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -49466,7 +50058,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J971" t="inlineStr"/>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>https://www.litasign.com/wp-content/uploads/2022/09/3d-metal-letters.jpg | https://shengenfab.com/wp-content/uploads/elementor/thumbs/Metal-Letters-Types-qykzp2wzt3ykf2l08zo5sz8aehlyw31syat37icyo8.jpg | https://shengenfab.com/wp-content/uploads/2024/12/Custom-Cast-Metal-Letters.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -49494,8 +50090,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F972" t="inlineStr"/>
-      <c r="G972" t="inlineStr"/>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Letra S de metal, utilizada para sinalização ou decoração.</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>Material: Metal; Tamanho: 145mm.</t>
+        </is>
+      </c>
       <c r="H972" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49506,7 +50110,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J972" t="inlineStr"/>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>https://www.fermoplast.com.br/app/assets/images/dinamica/produto/360/cor_0/aml-s-145mm-letra-s-230318-6edac2.jpg | https://img.freepik.com/fotos-premium/letra-s-em-maiuscula-de-metal-isolada-em-fundo-branco-3d-simbolo-de-letras-de-alfabeto-metalico_925819-8342.jpg?w=996 | https://cdn.litoarte.com.br/lalk/lalk-019.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -49594,7 +50202,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J974" t="inlineStr"/>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>https://equipamentos.mogiglass.com.br/wp-content/uploads/2021/09/9ee5ac1f013338333ab4bb4a3be40e81-9-1.jpg | https://img.lojadomecanico.com.br/IMAGENS/46/448/419569/1667240296674.JPG | https://images.tcdn.com.br/img/img_prod/746636/macho_manual_ao_liga_m3x05_graff_vantage_1_20260310154208_9d0e16d20cc3.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -49642,7 +50254,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J975" t="inlineStr"/>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>http://www.guimepa.com.br/cdn/shop/files/macho-manual-de-aco-r_pido-4-mm-x-0_7-mm-ma-jogo-com-2-pecas-vonder-plus-4358204007-1095497-_2.jpg?v=1758048754 | https://images.tcdn.com.br/img/img_prod/1359496/macho_manual_aco_liga_ws_m_4x0_7_rocast_14627_1_45b723e4a2087e0f519782bc53ab5b05.png | https://img.lojadomecanico.com.br/IMAGENS/37/320/135167/1646061344005.JPG</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -49738,7 +50354,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J977" t="inlineStr"/>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>https://cdn.leroymerlin.com.br/products/macho_manual_ar_3x0,50_ma_jogo_2_pecas_vonder_89391526_0001_600x600.jpg | https://img.lojadomecanico.com.br/IMAGENS/46/448/419569/1667240296917.JPG | https://delupo.vtexassets.com/arquivos/ids/168424/77420_01.jpg?v=637889370924530000</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -49771,7 +50391,11 @@
           <t>MACHO WW AC 3/16 * - Conector elétrico para aplicações específicas.</t>
         </is>
       </c>
-      <c r="G978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>Diâmetro: 3/16 polegadas, Tipo: Macho, Material: Aço Carbono.</t>
+        </is>
+      </c>
       <c r="H978" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49782,7 +50406,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J978" t="inlineStr"/>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7r98o-mc9dcm2vi38r27 | https://img.lojadomecanico.com.br/IMAGENS/46/448/419584/1667240334563.JPG | https://http2.mlstatic.com/D_NQ_NP_819698-MLB93733767787_092025-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -49810,8 +50438,16 @@
           <t>INATIVO</t>
         </is>
       </c>
-      <c r="F979" t="inlineStr"/>
-      <c r="G979" t="inlineStr"/>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Macho manual de aço liga, tamanho 3/8 polegadas, com 16 fpp (filetes por polegada), modelo AC 3/8, da marca RocaST.</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>Tamanho: 3/8 polegadas, Material: Aço Liga, Fpp: 16, Tipo: Macho Manual</t>
+        </is>
+      </c>
       <c r="H979" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -49822,7 +50458,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J979" t="inlineStr"/>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/746636/macho_manual_aco_liga_3_8pol_18fpp_npt_rocast_6607_1_5b1c42ad783b7f9dbb1ac83503feab45.jpg | https://images.tcdn.com.br/img/img_prod/1088369/macho_manual_aco_liga_ws_unc_38_16_fpp_2_pecas_rocast_2137_3_9281a56db51140318a968db7bbba80bb.jpg | https://images.tcdn.com.br/img/img_prod/1088369/macho_manual_aco_liga_ws_unc_38_16_fpp_2_pecas_rocast_2137_4_acf97ec5f99ad6e707a17dd9d74f422c.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -49918,7 +50558,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J981" t="inlineStr"/>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>https://d3ugyf2ht6aenh.cloudfront.net/stores/001/546/946/products/d_nq_np_2x_895616-mla44807279333_022021-f91-bccc15ac2cbba7191316161574983366-1024-1024.png | https://shoppingdocaminhoneiro.vtexassets.com/arquivos/ids/275698/image-6788b5694f5946acb7233496648e18dd.jpg?v=637769003907370000 | https://cdn.leroymerlin.com.br/products/macho_manual_ar_g__5_16_unc_jogo_2_pecas_vonder_89391540_0001_600x600.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -49966,7 +50610,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J982" t="inlineStr"/>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/br-11134207-7qukw-ljmsq6uvu2yy16 | https://palaciodasferramentas.com.br/media/catalog/product/1/_/1_1900.jpg?optimize=high&amp;bg-color=255,255,255&amp;fit=bounds&amp;height=600&amp;width=600&amp;canvas=600:600 | https://product-hub-prd.madeiramadeira.com.br/708531237/images/c058083d-c7d8-498f-b1be-ed92f578479a579ef4c110d68a992deb27cdd3.png</t>
+        </is>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -50010,7 +50658,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J983" t="inlineStr"/>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>https://down-br.img.susercontent.com/file/sg-11134201-7rd4w-lx005tkq84lk4d | https://down-br.img.susercontent.com/file/br-11134207-7r98o-m9eqyom6h2yh12 | https://http2.mlstatic.com/D_NQ_NP_953123-MLB81534324387_122024-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -50043,7 +50695,11 @@
           <t>Máscara de solda automática OptiArc 120, equipamento de proteção para soldagem.</t>
         </is>
       </c>
-      <c r="G984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>Escurecimento dinâmico de 5 a 13, ajuste de sensibilidade e atraso de desligamento.</t>
+        </is>
+      </c>
       <c r="H984" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -50054,7 +50710,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J984" t="inlineStr"/>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/694151/mascara_de_solda_automatica_optiarc_120_com_escurecimento_din_5_a_13_boxer_37511_3_176dd5a4d19deaffed5659f4e1fe4148.jpg | https://cdn.awsli.com.br/2500x2500/2604/2604930/produto/378047044/af636a329d57a00ec7f6f504e07b4e2a-q2sbnuig1h.jpg | https://product-hub-prd.madeiramadeira.com.br/934937/images/bc4ea233-dabf-4783-84a5-e8438f960b20ptiarc1201724877669200zoom.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -50098,7 +50758,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J985" t="inlineStr"/>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>https://cdn.b4c.inf.br/storage/universodasferragens/1000/mascara-de-solda-automatica-spectra-180-boxer-LVKP1757430223bgHw.jpg | https://cdn.awsli.com.br/2500x2500/1637/1637516/produto/378213270/captura-de-tela-2025-10-31-135118-mqosi1hx0u.png | https://cdn.b4c.inf.br/storage/universodasferragens/1000/mascara-de-solda-automatica-spectra-180-boxer-DO2R1757430223jjLQ.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -50142,7 +50806,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J986" t="inlineStr"/>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>https://img.lojadomecanico.com.br/IMAGENS/46/448/600848/1714673608958.JPG | https://img.lojadomecanico.com.br/IMAGENS/46/448/600848/1714673610828.JPG | https://down-br.img.susercontent.com/file/br-11134207-7r98o-lvkix9aa7qxb03</t>
+        </is>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -50190,7 +50858,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J987" t="inlineStr"/>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>https://loja.tenax.com.br/cdn/shop/files/viga-perfil-i-tenax-478148350_24bbfb2e-122f-480f-a93d-1fd2efec3e72.jpg?v=1705350509 | https://www.pessoaacos.com.br/wp-content/uploads/2025/05/fornecedor-perfil-w-2-9-1024x702.jpeg | http://coferpon.com.br/wp-content/uploads/2021/12/perfil-i-300x300.png</t>
+        </is>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -50238,7 +50910,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J988" t="inlineStr"/>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>https://loja.tenax.com.br/cdn/shop/files/viga-perfil-i-tenax-478148350_24bbfb2e-122f-480f-a93d-1fd2efec3e72.jpg?v=1705350509 | https://www.pessoaacos.com.br/wp-content/uploads/2025/05/fornecedor-perfil-w-2-9-1024x702.jpeg | https://imgv2-2-f.scribdassets.com/img/document/427147241/original/3465325036/1?v=1</t>
+        </is>
+      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -50286,7 +50962,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J989" t="inlineStr"/>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>https://loja.tenax.com.br/cdn/shop/files/viga-perfil-i-tenax-478148350_24bbfb2e-122f-480f-a93d-1fd2efec3e72.jpg?v=1705350509 | http://coferpon.com.br/wp-content/uploads/2021/12/perfil-i-300x300.png | https://usimg.bjyyb.net/sites/95500/95719/1750843043796427207052275712.png</t>
+        </is>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
@@ -50382,7 +51062,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J991" t="inlineStr"/>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>https://ciadoferro.com.br/wp-content/uploads/2022/02/perfilw-01-768x721.png | https://acotel.com.br/wp-content/uploads/2026/01/Capa-blog.jpg | https://www.comercialgoldoni.com.br/assets/uploads/produtos/fotos/f2f3a-GO_1816-baixa.png</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
@@ -50430,7 +51114,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J992" t="inlineStr"/>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>https://cdn.iset.io/assets/54735/produtos/26634/sapata_retangular_2.png | https://http2.mlstatic.com/D_NQ_NP_985389-MLB44296061552_122020-O.webp | https://cdn.iset.io/assets/54735/produtos/26634/sapata_retangular_3.png</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -50478,7 +51166,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J993" t="inlineStr"/>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>https://casanur.com.br/media/catalog/product/cache/9/small_image/420x/602f0fa2c1f0d1ba5e241f914e856ff9/h/t/https___images.madeiramadeira.com.br_product_images_64640468-rodaforro-pvc-premium-branco-6m-plasbil89932-803-1-600x600.jpg | https://casanur.com.br/media/catalog/product/cache/9/small_image/840x/602f0fa2c1f0d1ba5e241f914e856ff9/h/t/https___images.madeiramadeira.com.br_product_images_64640468-rodaforro-pvc-premium-branco-6m-plasbil89932-803-1-600x600.jpg | https://images.tcdn.com.br/img/img_prod/763413/roda_forro_pvc_tipo_colonial_branco_mais_pvc_pecas_com_6_00mts_1833_1_20200404095150.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
@@ -50526,7 +51218,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J994" t="inlineStr"/>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>https://s3.satintas.com.br/wp-content/uploads/2022/10/18112610/comprar-tinta-spray-chemicolor-uso-geral-verde-claro-satintas-loja-online-tintas-promocao.jpg | https://lfmaquinaseferramentas.vtexassets.com/arquivos/ids/242458/tinta-spray-uso-geral-chemicolor-verde-escuro-400ml_01.jpg?v=638609927506930000 | https://lfmaquinaseferramentas.vtexassets.com/arquivos/ids/242486/tinta-spray-uso-geral-chemicolor-verde-claro-400ml_01.jpg?v=638610467681000000</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -50574,7 +51270,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J995" t="inlineStr"/>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>https://r4nautic.com/wp-content/uploads/2018/09/5508-colorgin-uso-geral-premium-amarelo-6055891.jpg | https://elastobor.vteximg.com.br/arquivos/ids/182136-1000-1000/TINTA-COLORGIN-SPRAY-USO-GERAL-AMARELO--400ML.jpg?v=637130679475470000 | https://www.casacombate.com/media/catalog/product/cache/1/image/800x/17f82f742ffe127f42dca9de82fb58b1/c/o/colorgin_ug_am_400ml_55081_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -50622,7 +51322,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J996" t="inlineStr"/>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/1000x1000/1373/1373016/produto/57998373/60acce788a.jpg | https://www.construnok.com.br/uploads/construnok/produtos_imagens/image-2025-07-31T1534001753986851936449944.png | https://elastobor.vteximg.com.br/arquivos/ids/182132-500-500/TINTA-COLORGIN-SPRAY-USO-GERAL-AZUL-400ML.jpg?v=637130677696800000</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -50670,7 +51374,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J997" t="inlineStr"/>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>https://elastobor.vteximg.com.br/arquivos/ids/251792-500-500/TINTA-SPRAY-COLORGIN-USO-GERAL-BRANCA-400ML-KIT-COM-12UN.jpg?v=638042976800830000 | https://cdn.awsli.com.br/600x450/1373/1373016/produto/58281982/f447be8821.jpg | https://http2.mlstatic.com/D_NQ_NP_782326-MLB44140487801_112020-O.webp</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -50718,7 +51426,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J998" t="inlineStr"/>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>https://images.tcdn.com.br/img/img_prod/1086068/tinta_spray_vermelho_uso_geral_400ml_colorgin_55061_264670_1_7516b650ca5a966a4a48721601a599ac.png | https://bemol.vtexassets.com/arquivos/ids/261851/223210_b.jpg?v=638538137213230000 | https://elastobor.vteximg.com.br/arquivos/ids/198484-500-500/TINTA-SPRAY-COLORGIN-USO-GERAL-VERMELHA-400ML.jpg?v=637391444753400000</t>
+        </is>
+      </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
@@ -50751,7 +51463,11 @@
           <t>Steel Deck 0,80 é um produto cujas informações não puderam ser obtidas devido a um erro na busca na web.</t>
         </is>
       </c>
-      <c r="G999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>Espessura: 0,80mm, Material: Aço galvanizado</t>
+        </is>
+      </c>
       <c r="H999" t="inlineStr">
         <is>
           <t>Não encontrado</t>
@@ -50762,7 +51478,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J999" t="inlineStr"/>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>https://5.imimg.com/data5/SELLER/Default/2022/10/BV/XV/WY/1112067/steel-decking-sheet-slab-thickness-0-80mm-1000x1000.jpg | https://forteferroeaco.com.br/wp-content/uploads/2025/06/Steel-Deck-Ferro-Forte-e-Aco.webp | https://5.imimg.com/data5/SELLER/Default/2020/8/GV/HP/RL/898270/capture2-1000x1000.JPG</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -50810,7 +51530,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J1000" t="inlineStr"/>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>https://www.comercialgoldoni.com.br/assets/uploads/produtos/fotos/747e0-Marca-dagua-Goldoni.jpg | https://www.comercialgoldoni.com.br/assets/uploads/produtos/fotos/d00f7-4-1.png | https://metalsem.com.co/wp-content/uploads/2026/03/WhatsApp-Image-2026-03-26-at-08.32.11.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
@@ -50858,7 +51582,11 @@
           <t>Não encontrado</t>
         </is>
       </c>
-      <c r="J1001" t="inlineStr"/>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>https://cdn.awsli.com.br/300x300/1697/1697657/produto/135025361/916c51c7e3.jpg | https://www.comercialgoldoni.com.br/assets/uploads/produtos/fotos/b3ab4-5-1.png | https://i.ytimg.com/vi/w901hx6CYuM/maxresdefault.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
